--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -3062,7 +3062,7 @@
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Perfil AGN consultable y descargable en Excel: GET /api/perfil-agn, /api/perfil-agn/catalogo.xlsx.</t>
+          <t>Reglas del AGN como lógica del sistema; correspondencias por API: GET /api/calidad/correspondencias(.xlsx).</t>
         </is>
       </c>
     </row>

--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -9,24 +9,25 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requisitos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modulos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entidades_RiC" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pruebas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria_Claude" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AGN_RiC_RICORA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Erratas_AGN" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallazgos_generales" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierres" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modulos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entidades_RiC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flujos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pruebas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoria_Claude" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AGN_RiC_RICORA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Erratas_AGN" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallazgos_generales" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requisitos'!$A$1:$K$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modulos'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Entidades_RiC'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Flujos'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Pruebas'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fuentes'!$A$1:$C$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Auditoria_Claude'!$A$1:$I$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modulos'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Entidades_RiC'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Flujos'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Pruebas'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fuentes'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Auditoria_Claude'!$A$1:$I$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +498,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>4 de octubre de 2026</t>
+          <t>Auditoría: 4 de octubre de 2026 · actualizada con los cierres de la hoja «Cierres»</t>
         </is>
       </c>
     </row>
@@ -532,7 +533,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +563,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -663,6 +664,4327 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Capa</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Origen AGN</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Entidad</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Elemento</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Código citado por el AGN</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>¿Código del AGN correcto?</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Obligatoriedad AGN</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Regla AGN</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>RiC-CM 1.0 (correcto)</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>RiC-O 1.1</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Campo en RICORA</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Nivel de madurez</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REC-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 3</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Identificador único</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ric:identifier</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Formato CO-{ENTIDAD}-{SERIE}-{NÚMERO}, máximo 50 caracteres</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A22 Identifier</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>rico:identifier</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>codigo_referencia (código del CCD, compuesto desde el nivel superior) y URI persistente urn:uuid</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>El código del CCD sí es obligatorio (Acuerdo 001 de 2024); el formato CO-… del AGN es un ejemplo de un instrumento no obligatorio y no se impone. La medición de calidad avisa si pasa de 50 caracteres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 3</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Título formal</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>ric:name</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Máximo 255 caracteres, sin abreviaciones</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A28 Name (rico:title)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>rico:title</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>RICORA admite hasta 300 caracteres (ISAD-G no limita); la medición avisa si pasa de 255. rico:name existe; rico:title es su especialización para documentos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REC-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción del contenido</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ric:description</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Entre 50 y 500 caracteres</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A38 Scope and Content</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>rico:scopeAndContent</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>alcance_contenido</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>«ric:description» no existe en RiC-O 1.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REC-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Tipo de documento</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ric:hasDocumentaryFormType</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Vocabulario de la TRD más el vocabulario COAR</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A17 Documentary Form Type</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasDocumentaryFormType, rico:DocumentaryFormType</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>forma_documental_id (vocabulario del fondo, SKOS)</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>El AGN lo hace corresponder con ISAD(G) 3.1.4 «Nivel de descripción», que es otra cosa: el nivel va en rico:hasRecordSetType o en la clase. COAR no se adopta (ver decisiones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REC-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Dimensiones físicas o lógicas</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ric:hasExtent</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Especificar la unidad de medida (folios, MB…)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A35 Record Resource Extent</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasExtent, rico:RecordResourceExtent, rico:recordResourceExtent</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>folios (unidad: folios) y tamaño de cada instanciación (bytes, páginas)</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REC-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Soporte del documento</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ric:hasCarrierType</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Tipo MIME para digitales, descripción normalizada para físicos</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A05 Carrier Type (de la Instantiation)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasCarrierType, rico:CarrierType</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>soporte (FUID) y, en cada instanciación, soporte del original o tipo MIME y formato PRONOM</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>En RiC el soporte es de la instanciación, no del documento: RICORA lo exporta en la Instantiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REC-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Idioma del documento</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ric:language</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>ISO 639-2, «spa» por defecto</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A25 Language</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasOrHadLanguage</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>idiomas (ISO 639-3)</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>«spa» es el mismo código en ISO 639-2/T y en 639-3; RICORA usa 639-3 porque distingue lenguas indígenas colombianas que 639-2 agrupa. No se pone «spa» por defecto: el idioma lo confirma una persona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ric:carrierType · RiC-P13</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Vocabulario controlado: papel, digital, microfilm, audiovisual</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A05 Carrier Type</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasCarrierType</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>instanciaciones.soporte (vocabulario cerrado) o formato del archivo</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-02</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Localización física (signatura topográfica)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ric:physicalLocation · RiC-P35</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Incluir signatura topográfica, depósito, estantería</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A27 Physical Location (en RiC-O es atributo del Lugar, no de la instanciación)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>ubicacion_fisica + deposito, estante, entrepano; caja y carpeta en el FUID</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Se guarda y sale en la ficha, el inventario y la ficha ISAD(G); no va al RDF porque RiC-O 1.1 no tiene propiedad de dato para la ubicación de una instanciación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-03</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Extensión</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ric:extent · RiC-P32</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Unidades normalizadas (MB, GB, cajas, legajos)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A23 Instantiation Extent</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>rico:instantiationExtent, rico:hasExtent</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>tamano_bytes, paginas (con su unidad en rico:Extent)</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-04</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Características técnicas</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ric:technicalCharacteristics · RiC-P28</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Formato, resolución, compresión, hash SHA-256; PUID de PRONOM</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A41 Technical Characteristics</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>rico:technicalCharacteristics</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>formato PRONOM (Siegfried), MIME, versión, páginas</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>El hash va en la nota de autenticidad (RiC-A03), no aquí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-05</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Evidencias de autenticidad</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>ric:hasAuthentication · RiC-P25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Firmas digitales (X.509), sellos, marcas de agua</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A03 Authenticity Note</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>rico:authenticityNote</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>huella SHA-256, verificaciones de fijeza y validación de formato (veraPDF, JHOVE)</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>No se verifican firmas digitales X.509 (Ley 527 de 1999).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-06</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Estado de conservación</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ric:conditionOfRecord · RiC-A17</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Bueno, Regular, Malo, Restaurado; documentar daños</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A31 Physical Characteristics</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>rico:physicalCharacteristicsNote</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>estado_conservacion (vocabulario del AGN) + caracteristicas_fisicas</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A17 es Documentary Form Type, no el estado de conservación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-07</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Técnica de producción</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>ric:hasProductionTechnique · RiC-P29</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Manuscrito, mecanografiado, impreso, nacido digital, digitalizado</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A33 Production Technique</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>rico:productionTechnique</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>solo «digitalizado»: la derivación desde el original físico (RiC-R014)</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Manuscrito, mecanografiado o impreso no se registran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-08</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Identificador</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ric:hasOrHadIdentifier · RiC-P1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>URI persistente, código de barras, signatura</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A22 Identifier</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>rico:identifier</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>urn:uuid y URI dereferenciable pública</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-09</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Vínculo con el documento</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ric:isOrWasCarrierOf · ric:instantiates · RiC-R66</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Vincular con el Record Resource</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R025 has or had instantiation</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasOrHadInstantiation, rico:isOrWasInstantiationOf</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>relación has_or_had_instantiation</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R066 es «is or was enforced by».</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AGN-INS-10</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Instanciación</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Condiciones de acceso (el AGN la llama «accesibilidad»)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ric:hasAccessibility · RiC-P38</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Público, Restringido, Confidencial; con fundamento legal</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A08 Conditions of Access</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>rico:conditionsOfAccess</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>declaración de derechos Ley 1712 (pública, clasificada, reservada con plazo) heredable</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>RICORA usa las categorías de la Ley 1712 (pública, clasificada, reservada); «restringido» y «confidencial» no son categorías legales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>AGN-AGE-01</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Agente</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Nombre autorizado</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>ric:name</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Forma completa; consultar autoridades nacionales</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A28 Name (rico:AgentName)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>rico:name, rico:hasOrHadAgentName, rico:AgentName</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>nombre y formas del nombre con vigencia (ISAAR-CPF)</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AGN-AGE-02</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Agente</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Tipo de agente</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>ric:agentType</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Person, Corporate Body, Family, Group</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Clases RiC-E08 a E13 (no es un atributo)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>rico:Person, rico:CorporateBody, rico:Family, rico:Group, rico:Position, rico:Mechanism</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>subtipo del agente → clase RiC-O</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>«ric:agentType» no existe en RiC-O 1.1; el tipo es la clase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>AGN-AGE-03</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 5</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Agente</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Identificador del agente</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>ric:identifier</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>ORCID para personas, ROR para instituciones</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A22 Identifier</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>rico:identifier</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>identificadores con esquema: interno, VIAF, Wikidata, ISNI, LCNAF, ORCID, ROR (owl:sameAs)</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>ORCID y ROR se validan con su dígito de control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>AGN-AGE-04</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Agente</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Historia institucional o biográfica</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>ric:description</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Resumen de actividades relevantes</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A21 History</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>rico:history</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>historia (ficha de autoridad)</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>AGN-AGE-05</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 5</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Agente</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Lugares</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>ric:hasPlace</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Coordenadas cuando sea relevante</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R075 has or had location (Lugar, E22)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasOrHadLocation, rico:Place</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>relación del agente con un lugar del vocabulario, con coordenadas</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>AGN-ACT-01</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 6</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Actividad</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Denominación, descripción y fechas</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ric:name · ric:description · ric:hasBeginningDate · ric:hasEndDate</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Terminología del mapa de procesos; ISO 8601</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E15 Activity; RiC-A28; RiC-R069 / RiC-R071</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>rico:Activity, rico:name, rico:hasBeginningDate, rico:hasEndDate</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>actividad del vocabulario con periodo EDTF, ejercida por un agente y regulada por un mandato</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>«ric:description» no existe; las fechas en RiC son entidades Fecha (E18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUN-01</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Función</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Función con su marco normativo</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Function (RiC-E08) · ric:hasLegalStatus</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Terminología del manual de funciones; citar las normas</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>RiC-CM 1.0 no tiene la entidad Función: se representa con Activity (E15) y Activity Type (A02); el marco normativo con Mandate (E17, RiC-R067)</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>rico:ActivityType, rico:hasActivityType, rico:Mandate, rico:authorizes</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>tipo de actividad (función de la TRD) con jerarquía SKOS y mandato que la autoriza</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>E08 es Persona. hasLegalStatus (A26) es el estatuto jurídico de un agente, no el marco de una función.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>AGN-PER-01</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Nombres, fechas de existencia y ocupación</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Person (RiC-E08) · ric:hasAppellation · ric:hasBirthDate · ric:hasOccupation</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Apellidos, Nombres; fecha de nacimiento solo si es relevante (Ley 1581)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E08 Person; RiC-A28; RiC-R070; RiC-A30 Occupation Type</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>rico:Person, rico:hasOrHadAgentName, rico:hasBirthDate, rico:hasOrHadOccupationOfType</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>persona con formas del nombre, existencia EDTF y cargos (RiC-E12)</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>La ocupación se expresa como cargo ocupado (Position), no como tipo de ocupación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>AGN-COR-01</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 9</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Entidad corporativa</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Denominación, fechas, mandato y estatuto</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Body (RiC-E11) · ric:hasOtherName · ric:hasMandate</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Denominación oficial según acto de creación; competencias legales</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E11 Corporate Body; RiC-A28; RiC-A26 Legal Status; RiC-R067 authorizes (desde el Mandato)</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>rico:CorporateBody, rico:hasOrHadAgentName, rico:hasOrHadLegalStatus, rico:authorizes</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>entidad corporativa con formas del nombre, estatuto jurídico, hitos y mandatos</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>«ric:hasOtherName» y «ric:hasMandate» no existen en RiC-O 1.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REL-01</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 10</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Jerárquica (forma parte / contiene)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>ric:isPartOf · ric:includes</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Para documentos que forman parte de expedientes</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R024 includes or included</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>rico:includesOrIncluded, rico:isOrWasIncludedIn</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>inclusión orgánica y adicionales</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REL-02</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 10</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Asociativa</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>ric:isAssociatedWith</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Documentos temáticamente relacionados</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R001 is related to</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>rico:isRelatedTo</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>relacionadas y secuencia (RiC-R008)</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AGN-REL-03</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 10</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Derivación (copias, extractos)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>ric:derivedFrom</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Para copias, extractos, transcripciones</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R012 has copy (entre documentos); RiC-R014 derivación (entre instanciaciones)</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasCopy, rico:hasOrHadDerivedInstantiation</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>derivación y migración entre instanciaciones; la copia entre documentos descritos no</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-01</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Código de serie o subserie</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P001: Identifier (no P29)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Persistencia en el SGDEA</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A22 Identifier</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>rico:identifier</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>codigo_referencia (CCD)</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-02</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Nombre de la serie o subserie</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E02: Record Set + RiC-P005: Name</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E03 Record Set; RiC-A28</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>rico:RecordSet, rico:title</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>titulo de la agrupación</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Record Set es E03; E02 es Record Resource.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-03</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Dependencia productora</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E04: Agent + RiC-R01: isCreatedBy</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Incluir NIT o código institucional</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E07 Agent; RiC-R027 has creator</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasCreator</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>relación has_creator al agente (con sus identificadores)</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>E04 es Record y R001 es «is related to».</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-04</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Fechas extremas</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P004: Date / RiC-P005: Date Range</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>ISO 8601</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E18 Date con RiC-A29 Normalized Value y RiC-A42 Date Type</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>rico:Date, rico:normalizedDateValue</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>fechas_extremas_edtf (EDTF, compatible con ISO 8601-2) y nodos Fecha</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>En RiC-CM 1.0 la fecha es una entidad, no un atributo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-05</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P013: Carrier Type</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Papel, Digital, Mixto</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A05 Carrier Type</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasCarrierType</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>soporte</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-06</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Acceso y restricción</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P018 / RiC-P019</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Vincular con la Ley 1712 y la Ley 1581</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A08 Conditions of Access; RiC-A09 Conditions of Use</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>rico:conditionsOfAccess, rico:conditionsOfUse</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>clasificación Ley 1712 + condiciones de uso + datos personales</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-07</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Frecuencia de uso</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P031: Record State (adaptación local)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Sin equivalente en RiC-CM: Record State (A39) es el estado de producción (original, copia, borrador)</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>frecuencia_consulta (columna del FUID)</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Se usa en el inventario; no se exporta a RDF para no desvirtuar rico:RecordState.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-08</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Valor documental y disposición final</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R07: Has Appraisal Decision + RiC-P025: Appraisal Type</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Compatible con la TVD</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E16 Rule (regla de retención) con RiC-R063 regulates or regulated</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>rico:Rule, rico:regulatesOrRegulated</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>regla de retención de la TRD heredada + valoracion</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>hasAppraisalDecision no existe en RiC-O 1.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-09</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Soporte de preservación</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E06: Instantiation + RiC-P035: Storage Location</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E06 Instantiation; la ubicación del almacenamiento es metadato de preservación (PREMIS storage), no de RiC</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>rico:Instantiation</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>almacén y segunda copia, en el AIP con PREMIS</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-10</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Volumen documental</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P002: Extent</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Indicar la unidad</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A35 Record Resource Extent</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>rico:recordResourceExtent, rico:RecordResourceExtent</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>folios, caja, carpeta</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Básico (modelo mínimo viable)</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-11</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Procedimiento o proceso asociado</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E12: Function + RiC-R12: Is Function Of</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Vincular con el mapa de procesos</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E15 Activity / RiC-A02 Activity Type; RiC-R033 documents</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>rico:documents, rico:ActivityType</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>actividad documentada y tipo de actividad (función)</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>E12 es Puesto (Position).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-12</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Serie antecedente o derivada</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R23: Precedes / RiC-R24: Follows</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R008 precedes or preceded</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>rico:precedesOrPreceded, rico:followsOrFollowed</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>secuencia</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>R023 es vínculo genético y R024 es inclusión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-13</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Productor antecedente o sucesor</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R05 / RiC-R06</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Fusiones o cambios institucionales</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R016 relación temporal entre agentes (has successor)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasSuccessor, rico:AgentTemporalRelation</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>relación has_successor con fecha</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>R005 es subdivisión de grupo y R006 es subevento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-14</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Palabras clave o temas</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P003: Subject</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Vocabularios del AGN o tesauros sectoriales</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R019 has or had subject</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasOrHadSubject</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>agentes, lugares y actividades mencionados (vocabulario controlado)</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-15</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P006: Description</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A43 General Description</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>rico:generalDescription</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-16</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Ubicación física o digital</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>RiC-P035: Storage Location</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>URI o ruta del SGDEA/OAIS</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Sin propiedad de dato en RiC-O 1.1 para una instanciación</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>caja, carpeta, signatura topográfica; ruta interna del almacén (no se publica)</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>La ruta del almacén no se publica por seguridad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>AGN-FUID-17</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Anexo 2</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>FUID</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Responsable de custodia</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E04: Agent + RiC-R09: Is Custodian Of</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Coincidir con el responsable del plan de preservación</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>RiC-R039 has or had holder</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>rico:hasOrHadHolder, rico:RecordResourceHoldingRelation</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>custodio del documento y de la instanciación, con fechas</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>R009 es precedencia en el tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>AGN-TRA-01</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>pp. 43 y 50</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Datos personales y sensibles</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Ley 1581 de 2012: minimización y control de acceso</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Sin equivalente en RiC</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>datos_personales (no contiene, personales, sensibles, de menores)</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>No se exporta a RDF. La medición avisa si un documento con datos sensibles o de menores queda público.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>AGN-TRA-02</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>pp. 18-19</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Accesibilidad</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Ley 1680 de 2013; WCAG 2.1; versiones accesibles y descripción alternativa</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Sin equivalente en RiC</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>nota_accesibilidad (sale en la ficha pública)</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>AGN-TRA-03</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>p. 41</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Metadatos de preservación</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>PREMIS</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Eventos, fijeza, formato, entorno</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Fuera de RiC: PREMIS 3.0</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>PREMIS 3.0 en el AIP, validado contra el XSD oficial</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>AGN-TRA-04</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>p. 73</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Validación de metadatos</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>XSD o SHACL</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Controles de calidad automáticos</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>RiC-O 1.1 con formas SHACL</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>validación SHACL de cada exportación y comprobación contra el OWL oficial</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>AGN-TRA-05</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>pp. 11-12</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Niveles de madurez e indicadores de calidad</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Modelo mínimo viable; KPI de calidad de metadatos</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>medición de calidad por documento y por fondo según este perfil</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>AGN-TRA-06</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>p. 44</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Perfiles de aplicación por tipología</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Recomendado</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Plantillas para expedientes contractuales, judiciales, pensionales</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>no existen plantillas por tipología</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Ausente</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>AGN-TRA-07</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>p. 38</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Firma digital</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Opcional</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Ley 527 de 1999; Decreto 2364 de 2012</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>RiC-A03 Authenticity Note</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>rico:authenticityNote</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>no se valida la firma; solo fijeza y formato</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Ausente</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>AGN-TRA-08</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Adaptación colombiana (AGN v1.4)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Tabla 3</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Vocabulario COAR de tipos de recurso</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Junto al vocabulario de la TRD</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>no se adopta</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>No adoptado (decisión)</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>COAR describe tipos de recursos de repositorios académicos (artículo, tesis), no tipos documentales de archivo; el tipo documental sale de la TRD del fondo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>RIC-EXT-01</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Decisión propia de RICORA</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Certeza, fuente y estado de cada relación</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>RiC-O 1.1: rico:Relation con relationCertainty, relationSource, relationState</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>rico:relationCertainty, rico:relationSource, rico:relationState</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>nodo de relación con certeza del motor y fuente</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Es RiC-O oficial; la decisión propia es exponer la certeza de la IA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>RIC-EXT-02</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Decisión propia de RICORA</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Mecanismo</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Programas y motor de IA como agentes con versión</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>RiC-E13 Mechanism; RiC-A41</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>rico:Mechanism, rico:technicalCharacteristics</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>vocabulario de mecanismos de solo lectura (OCR, PRONOM, motor)</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Avanzado</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>RIC-EXT-03</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Decisión propia de RICORA</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Origen y confianza de cada dato (motor o persona)</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Sin equivalente en RiC</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>origen_* y confianza_* en la descripción; la IA propone y la persona decide</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -919,7 +5241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1320,14 +5642,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>NO EXISTE</t>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Sin rastro de MFA/TOTP/WebAuthn en app/, frontend/src ni requirements.txt; login solo correo+contraseña (app/routers/auth.py:195).</t>
+          <t>[Lote 1] TOTP RFC 6238 con códigos de respaldo y obligatoriedad por rol: app/core/doble_factor.py, app/routers/auth.py (/login/segundo-factor, /perfil/doble-factor/*, /roles/{clave}/doble-factor, /usuarios/{id}/doble-factor/restablecer), migración 0033; tests/test_brechas_lote1.py (vectores RFC, ingreso en dos pasos, rol obligatorio, restablecimiento). || Auditoría inicial: Sin rastro de MFA/TOTP/WebAuthn en app/, frontend/src ni requirements.txt; login solo correo+contraseña (app/routers/auth.py:195).</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1338,7 +5660,7 @@
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>No hay segundo factor para administrador ni otros roles sensibles.</t>
+          <t>Cerrada en el Lote 1. Riesgo residual: Secreto TOTP en claro en la base; la obligatoriedad viene apagada y debe encenderse para el administrador.</t>
         </is>
       </c>
     </row>
@@ -2991,14 +7313,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Disparadores BEFORE UPDATE/DELETE/TRUNCATE en registro_auditoria (alembic/versions/0001_autenticacion_y_auditoria.py:93-109); sin rutas de edición; lectura por permiso propia/todo (app/core/permisos.py:80-89). Pruebas: tests/test_autenticacion.py::test_la_auditoria_no_se_puede_modificar_ni_borrar, tests/test_auditoria.py::test_ningun_evento_se_edita_ni_se_borra_por_ninguna_ruta. Sin encadenamiento de hashes ni sellado externo; el dueño de la BD puede desactivar el trigger.</t>
+          <t>[Lote 1] Cadena de huellas SHA-256 calculada por disparador (migración 0032); verificar_cadena y GET /api/auditoria/cadena; sello guardado en la revisión semanal; tests/test_brechas_lote1.py (alterar y borrar con el disparador desactivado). || Auditoría inicial: Disparadores BEFORE UPDATE/DELETE/TRUNCATE en registro_auditoria (alembic/versions/0001_autenticacion_y_auditoria.py:93-109); sin rutas de edición; lectura por permiso propia/todo (app/core/permisos.py:80-89). Pruebas: tests/test_autenticacion.py::test_la_auditoria_no_se_puede_modificar_ni_borrar, tests/test_auditoria.py::test_ningun_evento_se_edita_ni_se_borra_por_ninguna_ruta. Sin encadenamiento de hashes ni sellado externo; el dueño de la BD puede desactivar el trigger.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3009,7 +7331,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>La inmutabilidad depende de un trigger que el propietario de la base puede eliminar; no hay encadenamiento criptográfico ni anclaje externo que detecte manipulación.</t>
+          <t>Cerrada en el Lote 1. Riesgo residual: El dueño de la base podría rehacer toda la cadena entre revisiones; lo delata el sello anotado fuera.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +7426,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Respaldo pg_dump con SHA-256 y simulacro de restauración en BD efímera (app/servicios/respaldo.py:92-205; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella); /api/salud devuelve {'estado':'ok'} sin comprobar BD (app/main.py:84-86); logging.basicConfig a stdout (app/main.py:17); sin métricas; sin healthcheck del servicio web en docker-compose.yml.</t>
+          <t>[Lote 1 (avanza)] /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). || Auditoría inicial: Respaldo pg_dump con SHA-256 y simulacro de restauración en BD efímera (app/servicios/respaldo.py:92-205; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella); /api/salud devuelve {'estado':'ok'} sin comprobar BD (app/main.py:84-86); logging.basicConfig a stdout (app/main.py:17); sin métricas; sin healthcheck del servicio web en docker-compose.yml.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3115,7 +7437,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Faltan métricas, health check real (BD, almacenamiento, trabajador) y respaldo de los archivos del almacén (solo segunda copia en el mismo disco).</t>
+          <t>Faltan métricas, health check real (BD, almacenamiento, trabajador) y respaldo de los archivos del almacén (solo segunda copia en el mismo disco). Avance del Lote 1 (avanza): /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). Pendiente: Faltan métricas y el respaldo del almacén fuera del servidor (lote 2).</t>
         </is>
       </c>
     </row>
@@ -3157,7 +7479,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>bcrypt 12 rondas, JWT HS256 con clave ≥32 obligatoria (app/core/seguridad.py:19-135; app/main.py:20-23), bloqueo por intentos (tests/test_autenticacion.py::test_bloqueo_tras_intentos_fallidos), cabeceras nosniff/DENY (app/main.py:89-95), ClamAV, segunda copia ro. HTTPS opcional con retorno a HTTP y galleta no segura (deploy.yml, RICORA_GALLETA_SEGURA 0); sin CSP/HSTS; secretos en .env plano; sin cifrado en reposo; contraseña admin restablecida en cada despliegue; texto documental enviado a Gemini (app/servicios/motor.py:217).</t>
+          <t>[Lote 1 (avanza)] Segundo factor y auditoría encadenada. || Auditoría inicial: bcrypt 12 rondas, JWT HS256 con clave ≥32 obligatoria (app/core/seguridad.py:19-135; app/main.py:20-23), bloqueo por intentos (tests/test_autenticacion.py::test_bloqueo_tras_intentos_fallidos), cabeceras nosniff/DENY (app/main.py:89-95), ClamAV, segunda copia ro. HTTPS opcional con retorno a HTTP y galleta no segura (deploy.yml, RICORA_GALLETA_SEGURA 0); sin CSP/HSTS; secretos en .env plano; sin cifrado en reposo; contraseña admin restablecida en cada despliegue; texto documental enviado a Gemini (app/servicios/motor.py:217).</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3168,7 +7490,7 @@
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Despliegue admite HTTP plano, no hay CSP/HSTS, MFA ni cifrado en reposo, y se envía contenido documental a un servicio externo.</t>
+          <t>Despliegue admite HTTP plano, no hay CSP/HSTS, MFA ni cifrado en reposo, y se envía contenido documental a un servicio externo. Avance del Lote 1 (avanza): Segundo factor y auditoría encadenada. Pendiente: Faltan CSP/HSTS, quitar la caída a HTTP y el restablecimiento de la contraseña del administrador en cada despliegue (lote 3).</t>
         </is>
       </c>
     </row>
@@ -3618,7 +7940,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Panel de alertas en aplicación (app/routers/alertas.py; app/models/alerta.py) para integridad, respaldos, formatos; logs stdout (app/main.py:17); health check trivial /api/salud (app/main.py:84). Sin métricas, sin alertas externas (correo/pager) ni logs estructurados.</t>
+          <t>[Lote 1 (avanza)] /api/salud consultable sin sesión por un monitor externo gratuito. || Auditoría inicial: Panel de alertas en aplicación (app/routers/alertas.py; app/models/alerta.py) para integridad, respaldos, formatos; logs stdout (app/main.py:17); health check trivial /api/salud (app/main.py:84). Sin métricas, sin alertas externas (correo/pager) ni logs estructurados.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3629,7 +7951,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>La observabilidad se limita a alertas internas y logs básicos; no hay métricas ni alertamiento fuera de la aplicación.</t>
+          <t>La observabilidad se limita a alertas internas y logs básicos; no hay métricas ni alertamiento fuera de la aplicación. Avance del Lote 1 (avanza): /api/salud consultable sin sesión por un monitor externo gratuito. Pendiente: Falta configurar el monitor y las métricas.</t>
         </is>
       </c>
     </row>
@@ -3746,6 +8068,220 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Requisito</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Estado en la auditoría</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Estado ahora</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Evidencia del cierre</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RF-SEC-003</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Lote 1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>TOTP RFC 6238 con códigos de respaldo y obligatoriedad por rol: app/core/doble_factor.py, app/routers/auth.py (/login/segundo-factor, /perfil/doble-factor/*, /roles/{clave}/doble-factor, /usuarios/{id}/doble-factor/restablecer), migración 0033; tests/test_brechas_lote1.py (vectores RFC, ingreso en dos pasos, rol obligatorio, restablecimiento).</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Secreto TOTP en claro en la base; la obligatoriedad viene apagada y debe encenderse para el administrador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RF-AUD-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Lote 1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Cadena de huellas SHA-256 calculada por disparador (migración 0032); verificar_cadena y GET /api/auditoria/cadena; sello guardado en la revisión semanal; tests/test_brechas_lote1.py (alterar y borrar con el disparador desactivado).</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>El dueño de la base podría rehacer toda la cadena entre revisiones; lo delata el sello anotado fuera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RF-OPS-001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Lote 1 (avanza)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>/api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio).</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Faltan métricas y el respaldo del almacén fuera del servidor (lote 2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>NFR-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Lote 1 (avanza)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>/api/salud consultable sin sesión por un monitor externo gratuito.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Falta configurar el monitor y las métricas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>NFR-01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Lote 1 (avanza)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Segundo factor y auditoría encadenada.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Faltan CSP/HSTS, quitar la caída a HTTP y el restablecimiento de la contraseña del administrador en cada despliegue (lote 3).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4071,7 +8607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4633,7 +9169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4823,7 +9359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5196,7 +9732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5335,7 +9871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5505,26 +10041,22 @@
           <t>RF-SEC-003</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>NO EXISTE</t>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sin rastro de MFA/TOTP/WebAuthn en app/, frontend/src ni requirements.txt; login solo correo+contraseña (app/routers/auth.py:195).</t>
+          <t>[Lote 1] TOTP RFC 6238 con códigos de respaldo y obligatoriedad por rol: app/core/doble_factor.py, app/routers/auth.py (/login/segundo-factor, /perfil/doble-factor/*, /roles/{clave}/doble-factor, /usuarios/{id}/doble-factor/restablecer), migración 0033; tests/test_brechas_lote1.py (vectores RFC, ingreso en dos pasos, rol obligatorio, restablecimiento). || Auditoría inicial: Sin rastro de MFA/TOTP/WebAuthn en app/, frontend/src ni requirements.txt; login solo correo+contraseña (app/routers/auth.py:195).</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>No hay segundo factor para administrador ni otros roles sensibles.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Implementar TOTP (pyotp) con enrolamiento, códigos de recuperación y exigencia configurable por rol en la tabla roles.</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 1. Riesgo residual: Secreto TOTP en claro en la base; la obligatoriedad viene apagada y debe encenderse para el administrador.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -6556,26 +11088,22 @@
           <t>RF-AUD-002</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Disparadores BEFORE UPDATE/DELETE/TRUNCATE en registro_auditoria (alembic/versions/0001_autenticacion_y_auditoria.py:93-109); sin rutas de edición; lectura por permiso propia/todo (app/core/permisos.py:80-89). Pruebas: tests/test_autenticacion.py::test_la_auditoria_no_se_puede_modificar_ni_borrar, tests/test_auditoria.py::test_ningun_evento_se_edita_ni_se_borra_por_ninguna_ruta. Sin encadenamiento de hashes ni sellado externo; el dueño de la BD puede desactivar el trigger.</t>
+          <t>[Lote 1] Cadena de huellas SHA-256 calculada por disparador (migración 0032); verificar_cadena y GET /api/auditoria/cadena; sello guardado en la revisión semanal; tests/test_brechas_lote1.py (alterar y borrar con el disparador desactivado). || Auditoría inicial: Disparadores BEFORE UPDATE/DELETE/TRUNCATE en registro_auditoria (alembic/versions/0001_autenticacion_y_auditoria.py:93-109); sin rutas de edición; lectura por permiso propia/todo (app/core/permisos.py:80-89). Pruebas: tests/test_autenticacion.py::test_la_auditoria_no_se_puede_modificar_ni_borrar, tests/test_auditoria.py::test_ningun_evento_se_edita_ni_se_borra_por_ninguna_ruta. Sin encadenamiento de hashes ni sellado externo; el dueño de la BD puede desactivar el trigger.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>La inmutabilidad depende de un trigger que el propietario de la base puede eliminar; no hay encadenamiento criptográfico ni anclaje externo que detecte manipulación.</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Añadir hash encadenado (hash_previo, hash) por evento, rol de BD de la app sin privilegios de DDL, y exportación periódica firmada del último hash fuera del servidor.</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 1. Riesgo residual: El dueño de la base podría rehacer toda la cadena entre revisiones; lo delata el sello anotado fuera.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -6633,12 +11161,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Respaldo pg_dump con SHA-256 y simulacro de restauración en BD efímera (app/servicios/respaldo.py:92-205; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella); /api/salud devuelve {'estado':'ok'} sin comprobar BD (app/main.py:84-86); logging.basicConfig a stdout (app/main.py:17); sin métricas; sin healthcheck del servicio web en docker-compose.yml.</t>
+          <t>[Lote 1 (avanza)] /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). || Auditoría inicial: Respaldo pg_dump con SHA-256 y simulacro de restauración en BD efímera (app/servicios/respaldo.py:92-205; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella); /api/salud devuelve {'estado':'ok'} sin comprobar BD (app/main.py:84-86); logging.basicConfig a stdout (app/main.py:17); sin métricas; sin healthcheck del servicio web en docker-compose.yml.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Faltan métricas, health check real (BD, almacenamiento, trabajador) y respaldo de los archivos del almacén (solo segunda copia en el mismo disco).</t>
+          <t>Faltan métricas, health check real (BD, almacenamiento, trabajador) y respaldo de los archivos del almacén (solo segunda copia en el mismo disco). Avance del Lote 1 (avanza): /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). Pendiente: Faltan métricas y el respaldo del almacén fuera del servidor (lote 2).</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6667,4325 +11195,4 @@
   <autoFilter ref="A1:I40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O58"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Capa</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Origen AGN</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Entidad</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Elemento</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Código citado por el AGN</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>¿Código del AGN correcto?</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Obligatoriedad AGN</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Regla AGN</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>RiC-CM 1.0 (correcto)</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>RiC-O 1.1</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>Campo en RICORA</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Nivel de madurez</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REC-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 3</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Identificador único</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ric:identifier</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Formato CO-{ENTIDAD}-{SERIE}-{NÚMERO}, máximo 50 caracteres</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A22 Identifier</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>rico:identifier</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>codigo_referencia (código del CCD, compuesto desde el nivel superior) y URI persistente urn:uuid</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>El código del CCD sí es obligatorio (Acuerdo 001 de 2024); el formato CO-… del AGN es un ejemplo de un instrumento no obligatorio y no se impone. La medición de calidad avisa si pasa de 50 caracteres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REC-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 3</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Título formal</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>ric:name</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Máximo 255 caracteres, sin abreviaciones</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A28 Name (rico:title)</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>rico:title</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>titulo</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>RICORA admite hasta 300 caracteres (ISAD-G no limita); la medición avisa si pasa de 255. rico:name existe; rico:title es su especialización para documentos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REC-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Descripción del contenido</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>ric:description</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Entre 50 y 500 caracteres</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A38 Scope and Content</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>rico:scopeAndContent</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>alcance_contenido</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>«ric:description» no existe en RiC-O 1.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REC-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Tipo de documento</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>ric:hasDocumentaryFormType</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Vocabulario de la TRD más el vocabulario COAR</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A17 Documentary Form Type</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasDocumentaryFormType, rico:DocumentaryFormType</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>forma_documental_id (vocabulario del fondo, SKOS)</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>El AGN lo hace corresponder con ISAD(G) 3.1.4 «Nivel de descripción», que es otra cosa: el nivel va en rico:hasRecordSetType o en la clase. COAR no se adopta (ver decisiones).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REC-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 3</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Dimensiones físicas o lógicas</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>ric:hasExtent</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Especificar la unidad de medida (folios, MB…)</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A35 Record Resource Extent</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasExtent, rico:RecordResourceExtent, rico:recordResourceExtent</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>folios (unidad: folios) y tamaño de cada instanciación (bytes, páginas)</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REC-06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 3</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Soporte del documento</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>ric:hasCarrierType</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Tipo MIME para digitales, descripción normalizada para físicos</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A05 Carrier Type (de la Instantiation)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasCarrierType, rico:CarrierType</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>soporte (FUID) y, en cada instanciación, soporte del original o tipo MIME y formato PRONOM</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>En RiC el soporte es de la instanciación, no del documento: RICORA lo exporta en la Instantiation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REC-07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 3</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Idioma del documento</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>ric:language</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>ISO 639-2, «spa» por defecto</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A25 Language</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasOrHadLanguage</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>idiomas (ISO 639-3)</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>«spa» es el mismo código en ISO 639-2/T y en 639-3; RICORA usa 639-3 porque distingue lenguas indígenas colombianas que 639-2 agrupa. No se pone «spa» por defecto: el idioma lo confirma una persona.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>ric:carrierType · RiC-P13</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Vocabulario controlado: papel, digital, microfilm, audiovisual</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A05 Carrier Type</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasCarrierType</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>instanciaciones.soporte (vocabulario cerrado) o formato del archivo</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-02</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Localización física (signatura topográfica)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>ric:physicalLocation · RiC-P35</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Incluir signatura topográfica, depósito, estantería</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A27 Physical Location (en RiC-O es atributo del Lugar, no de la instanciación)</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>ubicacion_fisica + deposito, estante, entrepano; caja y carpeta en el FUID</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Se guarda y sale en la ficha, el inventario y la ficha ISAD(G); no va al RDF porque RiC-O 1.1 no tiene propiedad de dato para la ubicación de una instanciación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-03</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Extensión</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>ric:extent · RiC-P32</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Unidades normalizadas (MB, GB, cajas, legajos)</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A23 Instantiation Extent</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>rico:instantiationExtent, rico:hasExtent</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>tamano_bytes, paginas (con su unidad en rico:Extent)</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-04</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Características técnicas</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>ric:technicalCharacteristics · RiC-P28</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Formato, resolución, compresión, hash SHA-256; PUID de PRONOM</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A41 Technical Characteristics</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>rico:technicalCharacteristics</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>formato PRONOM (Siegfried), MIME, versión, páginas</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>El hash va en la nota de autenticidad (RiC-A03), no aquí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-05</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Evidencias de autenticidad</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>ric:hasAuthentication · RiC-P25</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Firmas digitales (X.509), sellos, marcas de agua</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A03 Authenticity Note</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>rico:authenticityNote</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>huella SHA-256, verificaciones de fijeza y validación de formato (veraPDF, JHOVE)</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>No se verifican firmas digitales X.509 (Ley 527 de 1999).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-06</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Estado de conservación</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>ric:conditionOfRecord · RiC-A17</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Bueno, Regular, Malo, Restaurado; documentar daños</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A31 Physical Characteristics</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>rico:physicalCharacteristicsNote</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>estado_conservacion (vocabulario del AGN) + caracteristicas_fisicas</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A17 es Documentary Form Type, no el estado de conservación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-07</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Técnica de producción</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>ric:hasProductionTechnique · RiC-P29</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Manuscrito, mecanografiado, impreso, nacido digital, digitalizado</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A33 Production Technique</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>rico:productionTechnique</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>solo «digitalizado»: la derivación desde el original físico (RiC-R014)</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Manuscrito, mecanografiado o impreso no se registran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-08</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Identificador</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>ric:hasOrHadIdentifier · RiC-P1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>URI persistente, código de barras, signatura</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A22 Identifier</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>rico:identifier</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>urn:uuid y URI dereferenciable pública</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-09</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Vínculo con el documento</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>ric:isOrWasCarrierOf · ric:instantiates · RiC-R66</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Vincular con el Record Resource</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R025 has or had instantiation</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasOrHadInstantiation, rico:isOrWasInstantiationOf</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>relación has_or_had_instantiation</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R066 es «is or was enforced by».</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>AGN-INS-10</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Instanciación</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Condiciones de acceso (el AGN la llama «accesibilidad»)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>ric:hasAccessibility · RiC-P38</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Público, Restringido, Confidencial; con fundamento legal</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A08 Conditions of Access</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>rico:conditionsOfAccess</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>declaración de derechos Ley 1712 (pública, clasificada, reservada con plazo) heredable</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>RICORA usa las categorías de la Ley 1712 (pública, clasificada, reservada); «restringido» y «confidencial» no son categorías legales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>AGN-AGE-01</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 5</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Agente</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Nombre autorizado</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>ric:name</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Forma completa; consultar autoridades nacionales</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A28 Name (rico:AgentName)</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>rico:name, rico:hasOrHadAgentName, rico:AgentName</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>nombre y formas del nombre con vigencia (ISAAR-CPF)</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>AGN-AGE-02</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 5</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Agente</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Tipo de agente</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>ric:agentType</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Person, Corporate Body, Family, Group</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Clases RiC-E08 a E13 (no es un atributo)</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>rico:Person, rico:CorporateBody, rico:Family, rico:Group, rico:Position, rico:Mechanism</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>subtipo del agente → clase RiC-O</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>«ric:agentType» no existe en RiC-O 1.1; el tipo es la clase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>AGN-AGE-03</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 5</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Agente</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Identificador del agente</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>ric:identifier</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>ORCID para personas, ROR para instituciones</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A22 Identifier</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>rico:identifier</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>identificadores con esquema: interno, VIAF, Wikidata, ISNI, LCNAF, ORCID, ROR (owl:sameAs)</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>ORCID y ROR se validan con su dígito de control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>AGN-AGE-04</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 5</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Agente</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Historia institucional o biográfica</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>ric:description</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Resumen de actividades relevantes</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A21 History</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>rico:history</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>historia (ficha de autoridad)</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>AGN-AGE-05</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 5</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Agente</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Lugares</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>ric:hasPlace</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Coordenadas cuando sea relevante</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R075 has or had location (Lugar, E22)</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasOrHadLocation, rico:Place</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>relación del agente con un lugar del vocabulario, con coordenadas</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>AGN-ACT-01</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 6</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Actividad</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Denominación, descripción y fechas</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>ric:name · ric:description · ric:hasBeginningDate · ric:hasEndDate</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Terminología del mapa de procesos; ISO 8601</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E15 Activity; RiC-A28; RiC-R069 / RiC-R071</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>rico:Activity, rico:name, rico:hasBeginningDate, rico:hasEndDate</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>actividad del vocabulario con periodo EDTF, ejercida por un agente y regulada por un mandato</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>«ric:description» no existe; las fechas en RiC son entidades Fecha (E18).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUN-01</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 7</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Función</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Función con su marco normativo</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Function (RiC-E08) · ric:hasLegalStatus</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Terminología del manual de funciones; citar las normas</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>RiC-CM 1.0 no tiene la entidad Función: se representa con Activity (E15) y Activity Type (A02); el marco normativo con Mandate (E17, RiC-R067)</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>rico:ActivityType, rico:hasActivityType, rico:Mandate, rico:authorizes</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>tipo de actividad (función de la TRD) con jerarquía SKOS y mandato que la autoriza</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>E08 es Persona. hasLegalStatus (A26) es el estatuto jurídico de un agente, no el marco de una función.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>AGN-PER-01</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 8</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Persona</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Nombres, fechas de existencia y ocupación</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Person (RiC-E08) · ric:hasAppellation · ric:hasBirthDate · ric:hasOccupation</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Apellidos, Nombres; fecha de nacimiento solo si es relevante (Ley 1581)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E08 Person; RiC-A28; RiC-R070; RiC-A30 Occupation Type</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>rico:Person, rico:hasOrHadAgentName, rico:hasBirthDate, rico:hasOrHadOccupationOfType</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>persona con formas del nombre, existencia EDTF y cargos (RiC-E12)</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>La ocupación se expresa como cargo ocupado (Position), no como tipo de ocupación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>AGN-COR-01</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 9</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Entidad corporativa</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Denominación, fechas, mandato y estatuto</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Corporate Body (RiC-E11) · ric:hasOtherName · ric:hasMandate</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Denominación oficial según acto de creación; competencias legales</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E11 Corporate Body; RiC-A28; RiC-A26 Legal Status; RiC-R067 authorizes (desde el Mandato)</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>rico:CorporateBody, rico:hasOrHadAgentName, rico:hasOrHadLegalStatus, rico:authorizes</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>entidad corporativa con formas del nombre, estatuto jurídico, hitos y mandatos</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>«ric:hasOtherName» y «ric:hasMandate» no existen en RiC-O 1.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REL-01</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 10</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Relación</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Jerárquica (forma parte / contiene)</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>ric:isPartOf · ric:includes</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Para documentos que forman parte de expedientes</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R024 includes or included</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>rico:includesOrIncluded, rico:isOrWasIncludedIn</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>inclusión orgánica y adicionales</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REL-02</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 10</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Relación</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Asociativa</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>ric:isAssociatedWith</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Documentos temáticamente relacionados</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R001 is related to</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>rico:isRelatedTo</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>relacionadas y secuencia (RiC-R008)</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>AGN-REL-03</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 10</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Relación</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Derivación (copias, extractos)</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>ric:derivedFrom</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Para copias, extractos, transcripciones</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R012 has copy (entre documentos); RiC-R014 derivación (entre instanciaciones)</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasCopy, rico:hasOrHadDerivedInstantiation</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>derivación y migración entre instanciaciones; la copia entre documentos descritos no</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-01</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Código de serie o subserie</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P001: Identifier (no P29)</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Persistencia en el SGDEA</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A22 Identifier</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>rico:identifier</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>codigo_referencia (CCD)</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-02</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Nombre de la serie o subserie</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E02: Record Set + RiC-P005: Name</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E03 Record Set; RiC-A28</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>rico:RecordSet, rico:title</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>titulo de la agrupación</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Record Set es E03; E02 es Record Resource.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-03</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Dependencia productora</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E04: Agent + RiC-R01: isCreatedBy</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Incluir NIT o código institucional</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E07 Agent; RiC-R027 has creator</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasCreator</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>relación has_creator al agente (con sus identificadores)</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>E04 es Record y R001 es «is related to».</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-04</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Fechas extremas</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P004: Date / RiC-P005: Date Range</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>ISO 8601</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E18 Date con RiC-A29 Normalized Value y RiC-A42 Date Type</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>rico:Date, rico:normalizedDateValue</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>fechas_extremas_edtf (EDTF, compatible con ISO 8601-2) y nodos Fecha</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>En RiC-CM 1.0 la fecha es una entidad, no un atributo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-05</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P013: Carrier Type</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Papel, Digital, Mixto</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A05 Carrier Type</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasCarrierType</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>soporte</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-06</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Acceso y restricción</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P018 / RiC-P019</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Vincular con la Ley 1712 y la Ley 1581</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A08 Conditions of Access; RiC-A09 Conditions of Use</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>rico:conditionsOfAccess, rico:conditionsOfUse</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>clasificación Ley 1712 + condiciones de uso + datos personales</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-07</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Frecuencia de uso</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P031: Record State (adaptación local)</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Sin equivalente en RiC-CM: Record State (A39) es el estado de producción (original, copia, borrador)</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>frecuencia_consulta (columna del FUID)</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>Se usa en el inventario; no se exporta a RDF para no desvirtuar rico:RecordState.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-08</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Valor documental y disposición final</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R07: Has Appraisal Decision + RiC-P025: Appraisal Type</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Compatible con la TVD</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E16 Rule (regla de retención) con RiC-R063 regulates or regulated</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>rico:Rule, rico:regulatesOrRegulated</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>regla de retención de la TRD heredada + valoracion</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>hasAppraisalDecision no existe en RiC-O 1.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-09</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Soporte de preservación</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E06: Instantiation + RiC-P035: Storage Location</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E06 Instantiation; la ubicación del almacenamiento es metadato de preservación (PREMIS storage), no de RiC</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>rico:Instantiation</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>almacén y segunda copia, en el AIP con PREMIS</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-10</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Volumen documental</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P002: Extent</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Indicar la unidad</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A35 Record Resource Extent</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>rico:recordResourceExtent, rico:RecordResourceExtent</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>folios, caja, carpeta</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>Básico (modelo mínimo viable)</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-11</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Procedimiento o proceso asociado</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E12: Function + RiC-R12: Is Function Of</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Vincular con el mapa de procesos</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E15 Activity / RiC-A02 Activity Type; RiC-R033 documents</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>rico:documents, rico:ActivityType</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>actividad documentada y tipo de actividad (función)</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>E12 es Puesto (Position).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-12</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Serie antecedente o derivada</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R23: Precedes / RiC-R24: Follows</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R008 precedes or preceded</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>rico:precedesOrPreceded, rico:followsOrFollowed</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>secuencia</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>R023 es vínculo genético y R024 es inclusión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-13</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Productor antecedente o sucesor</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R05 / RiC-R06</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Fusiones o cambios institucionales</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R016 relación temporal entre agentes (has successor)</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasSuccessor, rico:AgentTemporalRelation</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>relación has_successor con fecha</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>R005 es subdivisión de grupo y R006 es subevento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-14</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Palabras clave o temas</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P003: Subject</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Vocabularios del AGN o tesauros sectoriales</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R019 has or had subject</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasOrHadSubject</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>agentes, lugares y actividades mencionados (vocabulario controlado)</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-15</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P006: Description</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A43 General Description</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>rico:generalDescription</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>nota</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-16</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Ubicación física o digital</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>RiC-P035: Storage Location</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>URI o ruta del SGDEA/OAIS</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Sin propiedad de dato en RiC-O 1.1 para una instanciación</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>caja, carpeta, signatura topográfica; ruta interna del almacén (no se publica)</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>La ruta del almacén no se publica por seguridad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>AGN-FUID-17</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Anexo 2</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>FUID</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Responsable de custodia</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E04: Agent + RiC-R09: Is Custodian Of</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Coincidir con el responsable del plan de preservación</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>RiC-R039 has or had holder</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>rico:hasOrHadHolder, rico:RecordResourceHoldingRelation</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>custodio del documento y de la instanciación, con fechas</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>R009 es precedencia en el tiempo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>AGN-TRA-01</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>pp. 43 y 50</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Datos personales y sensibles</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Ley 1581 de 2012: minimización y control de acceso</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Sin equivalente en RiC</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>datos_personales (no contiene, personales, sensibles, de menores)</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>No se exporta a RDF. La medición avisa si un documento con datos sensibles o de menores queda público.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>AGN-TRA-02</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>pp. 18-19</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Accesibilidad</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Ley 1680 de 2013; WCAG 2.1; versiones accesibles y descripción alternativa</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Sin equivalente en RiC</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>nota_accesibilidad (sale en la ficha pública)</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>AGN-TRA-03</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>p. 41</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Metadatos de preservación</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>PREMIS</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Eventos, fijeza, formato, entorno</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Fuera de RiC: PREMIS 3.0</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>PREMIS 3.0 en el AIP, validado contra el XSD oficial</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>AGN-TRA-04</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>p. 73</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Validación de metadatos</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>XSD o SHACL</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>Controles de calidad automáticos</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>RiC-O 1.1 con formas SHACL</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>validación SHACL de cada exportación y comprobación contra el OWL oficial</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>AGN-TRA-05</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>pp. 11-12</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Niveles de madurez e indicadores de calidad</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Modelo mínimo viable; KPI de calidad de metadatos</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>medición de calidad por documento y por fondo según este perfil</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>AGN-TRA-06</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>p. 44</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Perfiles de aplicación por tipología</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Recomendado</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Plantillas para expedientes contractuales, judiciales, pensionales</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>no existen plantillas por tipología</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Ausente</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>AGN-TRA-07</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>p. 38</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Firma digital</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Ley 527 de 1999; Decreto 2364 de 2012</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>RiC-A03 Authenticity Note</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>rico:authenticityNote</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>no se valida la firma; solo fijeza y formato</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>Ausente</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>AGN-TRA-08</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Adaptación colombiana (AGN v1.4)</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Tabla 3</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Vocabulario COAR de tipos de recurso</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Junto al vocabulario de la TRD</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>no se adopta</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>No adoptado (decisión)</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>COAR describe tipos de recursos de repositorios académicos (artículo, tesis), no tipos documentales de archivo; el tipo documental sale de la TRD del fondo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>RIC-EXT-01</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Decisión propia de RICORA</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Relación</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Certeza, fuente y estado de cada relación</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>RiC-O 1.1: rico:Relation con relationCertainty, relationSource, relationState</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>rico:relationCertainty, rico:relationSource, rico:relationState</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>nodo de relación con certeza del motor y fuente</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Es RiC-O oficial; la decisión propia es exponer la certeza de la IA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>RIC-EXT-02</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Decisión propia de RICORA</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Mecanismo</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Programas y motor de IA como agentes con versión</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>RiC-E13 Mechanism; RiC-A41</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>rico:Mechanism, rico:technicalCharacteristics</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>vocabulario de mecanismos de solo lectura (OCR, PRONOM, motor)</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>Avanzado</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>RIC-EXT-03</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Decisión propia de RICORA</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Origen y confianza de cada dato (motor o persona)</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Sin equivalente en RiC</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>origen_* y confianza_* en la descripción; la IA propone y la persona decide</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>Intermedio</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -61,7 +61,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +71,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -533,128 +533,108 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NO CUMPLE</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NO EXISTE</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>17</v>
-      </c>
+          <t>Casos de prueba (12)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Casos de prueba (12)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr"/>
+          <t>CUMPLE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CUMPLE</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>11</v>
-      </c>
+          <t>Entidades RiC-CM (19)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Entidades RiC-CM (19)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr"/>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CUMPLE</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>2</v>
+          <t>Perfil AGN v1.4 (57 correspondencias)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Cubierto: 47, Parcial: 7, Ausente: 2, No adoptado (decisión): 1</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Códigos citados por el AGN que no corresponden a RiC</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Perfil AGN v1.4 (57 correspondencias)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Cubierto: 47, Parcial: 7, Ausente: 2, No adoptado (decisión): 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Códigos citados por el AGN que no corresponden a RiC</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
           <t>Erratas del esquema documentadas</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5493,12 +5473,12 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>El 'fondo' (RecursoDocumental nivel=fondo, app/models/recurso_documental.py:28,41) acota datos vía fondo_id en instanciaciones/vocabulario (app/models/instanciacion.py:34). No hay modelo Organización ni asignación usuario↔fondo; permisos por módulo, no por fondo (app/core/permisos.py:84-91). docker-compose.yml:2 'una instancia por entidad'.</t>
+          <t>[Decisión] Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto. || El 'fondo' (RecursoDocumental nivel=fondo, app/models/recurso_documental.py:28,41) acota datos vía fondo_id en instanciaciones/vocabulario (app/models/instanciacion.py:34). No hay modelo Organización ni asignación usuario↔fondo; permisos por módulo, no por fondo (app/core/permisos.py:84-91). docker-compose.yml:2 'una instancia por entidad'.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -5509,7 +5489,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>No existe separación de datos entre organizaciones ni restricción de acceso por fondo: cualquier usuario con permiso de módulo ve todos los fondos.</t>
+          <t>Fuera de alcance. Riesgo residual: Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5629,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1] TOTP RFC 6238 con códigos de respaldo y obligatoriedad por rol: app/core/doble_factor.py, app/routers/auth.py (/login/segundo-factor, /perfil/doble-factor/*, /roles/{clave}/doble-factor, /usuarios/{id}/doble-factor/restablecer), migración 0033; tests/test_brechas_lote1.py (vectores RFC, ingreso en dos pasos, rol obligatorio, restablecimiento). || Auditoría inicial: Sin rastro de MFA/TOTP/WebAuthn en app/, frontend/src ni requirements.txt; login solo correo+contraseña (app/routers/auth.py:195).</t>
+          <t>[Lote 1] TOTP RFC 6238 con códigos de respaldo y obligatoriedad por rol: app/core/doble_factor.py, app/routers/auth.py (/login/segundo-factor, /perfil/doble-factor/*, /roles/{clave}/doble-factor, /usuarios/{id}/doble-factor/restablecer), migración 0033; tests/test_brechas_lote1.py (vectores RFC, ingreso en dos pasos, rol obligatorio, restablecimiento). || Sin rastro de MFA/TOTP/WebAuthn en app/, frontend/src ni requirements.txt; login solo correo+contraseña (app/routers/auth.py:195).</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5842,7 +5822,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -5895,7 +5875,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -5948,7 +5928,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -6001,7 +5981,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -6308,7 +6288,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -6606,7 +6586,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -6659,7 +6639,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -6713,7 +6693,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -7211,7 +7191,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -7320,7 +7300,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1] Cadena de huellas SHA-256 calculada por disparador (migración 0032); verificar_cadena y GET /api/auditoria/cadena; sello guardado en la revisión semanal; tests/test_brechas_lote1.py (alterar y borrar con el disparador desactivado). || Auditoría inicial: Disparadores BEFORE UPDATE/DELETE/TRUNCATE en registro_auditoria (alembic/versions/0001_autenticacion_y_auditoria.py:93-109); sin rutas de edición; lectura por permiso propia/todo (app/core/permisos.py:80-89). Pruebas: tests/test_autenticacion.py::test_la_auditoria_no_se_puede_modificar_ni_borrar, tests/test_auditoria.py::test_ningun_evento_se_edita_ni_se_borra_por_ninguna_ruta. Sin encadenamiento de hashes ni sellado externo; el dueño de la BD puede desactivar el trigger.</t>
+          <t>[Lote 1] Cadena de huellas SHA-256 calculada por disparador (migración 0032); verificar_cadena y GET /api/auditoria/cadena; sello guardado en la revisión semanal; tests/test_brechas_lote1.py (alterar y borrar con el disparador desactivado). || Disparadores BEFORE UPDATE/DELETE/TRUNCATE en registro_auditoria (alembic/versions/0001_autenticacion_y_auditoria.py:93-109); sin rutas de edición; lectura por permiso propia/todo (app/core/permisos.py:80-89). Pruebas: tests/test_autenticacion.py::test_la_auditoria_no_se_puede_modificar_ni_borrar, tests/test_auditoria.py::test_ningun_evento_se_edita_ni_se_borra_por_ninguna_ruta. Sin encadenamiento de hashes ni sellado externo; el dueño de la BD puede desactivar el trigger.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -7419,14 +7399,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1 (avanza)] /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). || Auditoría inicial: Respaldo pg_dump con SHA-256 y simulacro de restauración en BD efímera (app/servicios/respaldo.py:92-205; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella); /api/salud devuelve {'estado':'ok'} sin comprobar BD (app/main.py:84-86); logging.basicConfig a stdout (app/main.py:17); sin métricas; sin healthcheck del servicio web en docker-compose.yml.</t>
+          <t>[Lote 2 (avanza)] Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO. || [Lote 1 (avanza)] /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). || Respaldo pg_dump con SHA-256 y simulacro de restauración en BD efímera (app/servicios/respaldo.py:92-205; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella); /api/salud devuelve {'estado':'ok'} sin comprobar BD (app/main.py:84-86); logging.basicConfig a stdout (app/main.py:17); sin métricas; sin healthcheck del servicio web en docker-compose.yml.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -7437,7 +7417,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Faltan métricas, health check real (BD, almacenamiento, trabajador) y respaldo de los archivos del almacén (solo segunda copia en el mismo disco). Avance del Lote 1 (avanza): /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). Pendiente: Faltan métricas y el respaldo del almacén fuera del servidor (lote 2).</t>
+          <t>Faltan métricas, health check real (BD, almacenamiento, trabajador) y respaldo de los archivos del almacén (solo segunda copia en el mismo disco). Avance del Lote 1 (avanza): /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). Pendiente: Faltan métricas y el respaldo del almacén fuera del servidor (lote 2). Avance del Lote 2 (avanza): Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO. Pendiente: Solo faltan métricas.</t>
         </is>
       </c>
     </row>
@@ -7472,14 +7452,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1 (avanza)] Segundo factor y auditoría encadenada. || Auditoría inicial: bcrypt 12 rondas, JWT HS256 con clave ≥32 obligatoria (app/core/seguridad.py:19-135; app/main.py:20-23), bloqueo por intentos (tests/test_autenticacion.py::test_bloqueo_tras_intentos_fallidos), cabeceras nosniff/DENY (app/main.py:89-95), ClamAV, segunda copia ro. HTTPS opcional con retorno a HTTP y galleta no segura (deploy.yml, RICORA_GALLETA_SEGURA 0); sin CSP/HSTS; secretos en .env plano; sin cifrado en reposo; contraseña admin restablecida en cada despliegue; texto documental enviado a Gemini (app/servicios/motor.py:217).</t>
+          <t>[Lote 1 (avanza)] Segundo factor y auditoría encadenada. || bcrypt 12 rondas, JWT HS256 con clave ≥32 obligatoria (app/core/seguridad.py:19-135; app/main.py:20-23), bloqueo por intentos (tests/test_autenticacion.py::test_bloqueo_tras_intentos_fallidos), cabeceras nosniff/DENY (app/main.py:89-95), ClamAV, segunda copia ro. HTTPS opcional con retorno a HTTP y galleta no segura (deploy.yml, RICORA_GALLETA_SEGURA 0); sin CSP/HSTS; secretos en .env plano; sin cifrado en reposo; contraseña admin restablecida en cada despliegue; texto documental enviado a Gemini (app/servicios/motor.py:217).</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -7623,14 +7603,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>NO EXISTE</t>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>No se encontró definición de RPO/RTO ni escenarios de disponibilidad en documentacion/ ni en código (grep RPO/RTO/'punto de recuperación' sin resultados). Despliegue de una sola instancia en un Droplet de 2 GB (app/main.py:2-4; deploy.yml).</t>
+          <t>[Lote 2] Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido. || No se encontró definición de RPO/RTO ni escenarios de disponibilidad en documentacion/ ni en código (grep RPO/RTO/'punto de recuperación' sin resultados). Despliegue de una sola instancia en un Droplet de 2 GB (app/main.py:2-4; deploy.yml).</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -7641,7 +7621,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>No hay objetivos de RPO/RTO por escenario ni arquitectura de disponibilidad asociada.</t>
+          <t>Cerrada en el Lote 2. Riesgo residual: El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
         </is>
       </c>
     </row>
@@ -7676,14 +7656,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>NO CUMPLE</t>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Un solo proceso uvicorn sin workers (docker-entrypoint.sh:45), almacenamiento en disco local (app/servicios/almacen.py), trabajador único que sondea la BD (app/trabajador.py), segunda copia en el mismo disco (docker-compose.yml comentarios de volúmenes). Solo tope de 300 nodos en grafo (app/servicios/grafo.py:40).</t>
+          <t>[Decisión] Fuera del alcance de la tesis por decisión acordada: el piloto corre en un solo servidor. || Un solo proceso uvicorn sin workers (docker-entrypoint.sh:45), almacenamiento en disco local (app/servicios/almacen.py), trabajador único que sondea la BD (app/trabajador.py), segunda copia en el mismo disco (docker-compose.yml comentarios de volúmenes). Solo tope de 300 nodos en grafo (app/servicios/grafo.py:40).</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -7694,7 +7674,7 @@
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>La arquitectura no escala horizontalmente ni separa almacenamiento de objetos.</t>
+          <t>Fuera de alcance. Riesgo residual: Para crecer: separar el almacén en un servicio de objetos y varios procesos web.</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7709,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -7782,14 +7762,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Restauración probada de la BD en base efímera (app/servicios/respaldo.py:128-192; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella, ::test_un_volcado_alterado_hace_fallar_el_simulacro_con_alerta) y de archivos desde segunda copia (tests/test_preservacion_oais.py::test_alteracion_de_la_primaria_se_restaura_desde_la_segunda_copia). No hay prueba de recuperación completa (BD + almacén) en otro servidor.</t>
+          <t>[Lote 2] Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py. || Restauración probada de la BD en base efímera (app/servicios/respaldo.py:128-192; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella, ::test_un_volcado_alterado_hace_fallar_el_simulacro_con_alerta) y de archivos desde segunda copia (tests/test_preservacion_oais.py::test_alteracion_de_la_primaria_se_restaura_desde_la_segunda_copia). No hay prueba de recuperación completa (BD + almacén) en otro servidor.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -7800,7 +7780,7 @@
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>No se ha probado la recuperación integral del sistema (base + archivos + configuración) en un entorno nuevo.</t>
+          <t>Cerrada en el Lote 2. Riesgo residual: El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
         </is>
       </c>
     </row>
@@ -7933,14 +7913,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1 (avanza)] /api/salud consultable sin sesión por un monitor externo gratuito. || Auditoría inicial: Panel de alertas en aplicación (app/routers/alertas.py; app/models/alerta.py) para integridad, respaldos, formatos; logs stdout (app/main.py:17); health check trivial /api/salud (app/main.py:84). Sin métricas, sin alertas externas (correo/pager) ni logs estructurados.</t>
+          <t>[Lote 1 (avanza)] /api/salud consultable sin sesión por un monitor externo gratuito. || Panel de alertas en aplicación (app/routers/alertas.py; app/models/alerta.py) para integridad, respaldos, formatos; logs stdout (app/main.py:17); health check trivial /api/salud (app/main.py:84). Sin métricas, sin alertas externas (correo/pager) ni logs estructurados.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -7986,7 +7966,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -8039,7 +8019,7 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -8073,7 +8053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8191,7 +8171,7 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -8223,7 +8203,7 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -8255,7 +8235,7 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -8273,6 +8253,166 @@
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Faltan CSP/HSTS, quitar la caída a HTTP y el restablecimiento de la contraseña del administrador en cada despliegue (lote 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>NFR-04</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>NO EXISTE</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Lote 2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>NFR-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lote 2</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RF-OPS-001</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Lote 2 (avanza)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Solo faltan métricas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RF-GOV-001</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>NFR-05</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>NO CUMPLE</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Fuera del alcance de la tesis por decisión acordada: el piloto corre en un solo servidor.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Para crecer: separar el almacén en un servicio de objetos y varios procesos web.</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9157,7 @@
           <t>Evento.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -9071,7 +9211,7 @@
           <t>Regla.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -9688,14 +9828,14 @@
           <t>Restaurar y comprobar integridad.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella (BD en base efímera, compara conteos y huella de fijeza); tests/test_preservacion_oais.py::test_alteracion_de_la_primaria_se_restaura_desde_la_segunda_copia. Falta restauración integral BD+almacén en entorno nuevo.</t>
+          <t>[Lote 2] tests/test_brechas_lote2.py::test_paquete_completo_se_restaura_entero_y_mide_el_tiempo y ::test_un_archivo_alterado_en_el_paquete_hace_fallar_la_restauracion (base + archivos + auditoría).</t>
         </is>
       </c>
     </row>
@@ -9946,24 +10086,20 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>El 'fondo' (RecursoDocumental nivel=fondo, app/models/recurso_documental.py:28,41) acota datos vía fondo_id en instanciaciones/vocabulario (app/models/instanciacion.py:34). No hay modelo Organización ni asignación usuario↔fondo; permisos por módulo, no por fondo (app/core/permisos.py:84-91). docker-compose.yml:2 'una instancia por entidad'.</t>
+          <t>[Decisión] Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto. || El 'fondo' (RecursoDocumental nivel=fondo, app/models/recurso_documental.py:28,41) acota datos vía fondo_id en instanciaciones/vocabulario (app/models/instanciacion.py:34). No hay modelo Organización ni asignación usuario↔fondo; permisos por módulo, no por fondo (app/core/permisos.py:84-91). docker-compose.yml:2 'una instancia por entidad'.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>No existe separación de datos entre organizaciones ni restricción de acceso por fondo: cualquier usuario con permiso de módulo ve todos los fondos.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Añadir entidad Organización/espacio y tabla usuario_fondo, y filtrar cada consulta por los fondos autorizados del actor en una dependencia común.</t>
-        </is>
-      </c>
+          <t>Fuera de alcance. Riesgo residual: Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -10048,7 +10184,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1] TOTP RFC 6238 con códigos de respaldo y obligatoriedad por rol: app/core/doble_factor.py, app/routers/auth.py (/login/segundo-factor, /perfil/doble-factor/*, /roles/{clave}/doble-factor, /usuarios/{id}/doble-factor/restablecer), migración 0033; tests/test_brechas_lote1.py (vectores RFC, ingreso en dos pasos, rol obligatorio, restablecimiento). || Auditoría inicial: Sin rastro de MFA/TOTP/WebAuthn en app/, frontend/src ni requirements.txt; login solo correo+contraseña (app/routers/auth.py:195).</t>
+          <t>[Lote 1] TOTP RFC 6238 con códigos de respaldo y obligatoriedad por rol: app/core/doble_factor.py, app/routers/auth.py (/login/segundo-factor, /perfil/doble-factor/*, /roles/{clave}/doble-factor, /usuarios/{id}/doble-factor/restablecer), migración 0033; tests/test_brechas_lote1.py (vectores RFC, ingreso en dos pasos, rol obligatorio, restablecimiento). || Sin rastro de MFA/TOTP/WebAuthn en app/, frontend/src ni requirements.txt; login solo correo+contraseña (app/routers/auth.py:195).</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -10161,7 +10297,7 @@
           <t>RF-OCR-001</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10204,7 +10340,7 @@
           <t>RF-OCR-002</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10247,7 +10383,7 @@
           <t>RF-RIC-001</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10290,7 +10426,7 @@
           <t>RF-RIC-002</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10468,7 +10604,7 @@
           <t>RF-AI-002</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10646,7 +10782,7 @@
           <t>RF-SEARCH-001</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10689,7 +10825,7 @@
           <t>RF-SEARCH-002</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -10732,7 +10868,7 @@
           <t>RF-PRES-001</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -11018,7 +11154,7 @@
           <t>RF-INT-003</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
@@ -11095,7 +11231,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1] Cadena de huellas SHA-256 calculada por disparador (migración 0032); verificar_cadena y GET /api/auditoria/cadena; sello guardado en la revisión semanal; tests/test_brechas_lote1.py (alterar y borrar con el disparador desactivado). || Auditoría inicial: Disparadores BEFORE UPDATE/DELETE/TRUNCATE en registro_auditoria (alembic/versions/0001_autenticacion_y_auditoria.py:93-109); sin rutas de edición; lectura por permiso propia/todo (app/core/permisos.py:80-89). Pruebas: tests/test_autenticacion.py::test_la_auditoria_no_se_puede_modificar_ni_borrar, tests/test_auditoria.py::test_ningun_evento_se_edita_ni_se_borra_por_ninguna_ruta. Sin encadenamiento de hashes ni sellado externo; el dueño de la BD puede desactivar el trigger.</t>
+          <t>[Lote 1] Cadena de huellas SHA-256 calculada por disparador (migración 0032); verificar_cadena y GET /api/auditoria/cadena; sello guardado en la revisión semanal; tests/test_brechas_lote1.py (alterar y borrar con el disparador desactivado). || Disparadores BEFORE UPDATE/DELETE/TRUNCATE en registro_auditoria (alembic/versions/0001_autenticacion_y_auditoria.py:93-109); sin rutas de edición; lectura por permiso propia/todo (app/core/permisos.py:80-89). Pruebas: tests/test_autenticacion.py::test_la_auditoria_no_se_puede_modificar_ni_borrar, tests/test_auditoria.py::test_ningun_evento_se_edita_ni_se_borra_por_ninguna_ruta. Sin encadenamiento de hashes ni sellado externo; el dueño de la BD puede desactivar el trigger.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -11154,19 +11290,19 @@
           <t>RF-OPS-001</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1 (avanza)] /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). || Auditoría inicial: Respaldo pg_dump con SHA-256 y simulacro de restauración en BD efímera (app/servicios/respaldo.py:92-205; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella); /api/salud devuelve {'estado':'ok'} sin comprobar BD (app/main.py:84-86); logging.basicConfig a stdout (app/main.py:17); sin métricas; sin healthcheck del servicio web en docker-compose.yml.</t>
+          <t>[Lote 2 (avanza)] Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO. || [Lote 1 (avanza)] /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). || Respaldo pg_dump con SHA-256 y simulacro de restauración en BD efímera (app/servicios/respaldo.py:92-205; tests/test_cierre_pre10.py::test_respaldo_con_simulacro_correcto_y_huella); /api/salud devuelve {'estado':'ok'} sin comprobar BD (app/main.py:84-86); logging.basicConfig a stdout (app/main.py:17); sin métricas; sin healthcheck del servicio web en docker-compose.yml.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Faltan métricas, health check real (BD, almacenamiento, trabajador) y respaldo de los archivos del almacén (solo segunda copia en el mismo disco). Avance del Lote 1 (avanza): /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). Pendiente: Faltan métricas y el respaldo del almacén fuera del servidor (lote 2).</t>
+          <t>Faltan métricas, health check real (BD, almacenamiento, trabajador) y respaldo de los archivos del almacén (solo segunda copia en el mismo disco). Avance del Lote 1 (avanza): /api/salud revisa base, almacén, latido del trabajador y último respaldo probado (app/servicios/salud.py; tests/test_brechas_lote1.py::test_salud_dice_que_falta_y_solo_la_base_tumba_el_servicio). Pendiente: Faltan métricas y el respaldo del almacén fuera del servidor (lote 2). Avance del Lote 2 (avanza): Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO. Pendiente: Solo faltan métricas.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">

--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -7459,7 +7459,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>[Lote 1 (avanza)] Segundo factor y auditoría encadenada. || bcrypt 12 rondas, JWT HS256 con clave ≥32 obligatoria (app/core/seguridad.py:19-135; app/main.py:20-23), bloqueo por intentos (tests/test_autenticacion.py::test_bloqueo_tras_intentos_fallidos), cabeceras nosniff/DENY (app/main.py:89-95), ClamAV, segunda copia ro. HTTPS opcional con retorno a HTTP y galleta no segura (deploy.yml, RICORA_GALLETA_SEGURA 0); sin CSP/HSTS; secretos en .env plano; sin cifrado en reposo; contraseña admin restablecida en cada despliegue; texto documental enviado a Gemini (app/servicios/motor.py:217).</t>
+          <t>[Lote 3 (avanza)] HTTPS sin dominio propio (sslip.io + Let's Encrypt con Caddy), sin caída silenciosa a HTTP (aviso en el despliegue, franja en la interfaz y salud «degradado»), CSP y HSTS solo con HTTPS (app/main.py), contraseña del administrador solo al crear o con RICORA_ADMIN_RESTABLECER=1 (app/cli.py); tests/test_brechas_lote3.py, frontend/src/pruebas/sinCifrar.test.ts. || [Lote 1 (avanza)] Segundo factor y auditoría encadenada. || bcrypt 12 rondas, JWT HS256 con clave ≥32 obligatoria (app/core/seguridad.py:19-135; app/main.py:20-23), bloqueo por intentos (tests/test_autenticacion.py::test_bloqueo_tras_intentos_fallidos), cabeceras nosniff/DENY (app/main.py:89-95), ClamAV, segunda copia ro. HTTPS opcional con retorno a HTTP y galleta no segura (deploy.yml, RICORA_GALLETA_SEGURA 0); sin CSP/HSTS; secretos en .env plano; sin cifrado en reposo; contraseña admin restablecida en cada despliegue; texto documental enviado a Gemini (app/servicios/motor.py:217).</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Despliegue admite HTTP plano, no hay CSP/HSTS, MFA ni cifrado en reposo, y se envía contenido documental a un servicio externo. Avance del Lote 1 (avanza): Segundo factor y auditoría encadenada. Pendiente: Faltan CSP/HSTS, quitar la caída a HTTP y el restablecimiento de la contraseña del administrador en cada despliegue (lote 3).</t>
+          <t>Despliegue admite HTTP plano, no hay CSP/HSTS, MFA ni cifrado en reposo, y se envía contenido documental a un servicio externo. Avance del Lote 1 (avanza): Segundo factor y auditoría encadenada. Pendiente: Faltan CSP/HSTS, quitar la caída a HTTP y el restablecimiento de la contraseña del administrador en cada despliegue (lote 3). Avance del Lote 3 (avanza): HTTPS sin dominio propio (sslip.io + Let's Encrypt con Caddy), sin caída silenciosa a HTTP (aviso en el despliegue, franja en la interfaz y salud «degradado»), CSP y HSTS solo con HTTPS (app/main.py), contraseña del administrador solo al crear o con RICORA_ADMIN_RESTABLECER=1 (app/cli.py); tests/test_brechas_lote3.py, frontend/src/pruebas/sinCifrar.test.ts. Pendiente: Pasa a CUMPLE cuando el despliegue confirme el certificado; si el puerto 443 está cerrado en el cortafuegos, hay que abrirlo.</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8259,44 +8259,44 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>NFR-01</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>NO EXISTE</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>CUMPLE</t>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lote 2</t>
+          <t>Lote 3 (avanza)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
+          <t>HTTPS sin dominio propio (sslip.io + Let's Encrypt con Caddy), sin caída silenciosa a HTTP (aviso en el despliegue, franja en la interfaz y salud «degradado»), CSP y HSTS solo con HTTPS (app/main.py), contraseña del administrador solo al crear o con RICORA_ADMIN_RESTABLECER=1 (app/cli.py); tests/test_brechas_lote3.py, frontend/src/pruebas/sinCifrar.test.ts.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
+          <t>Pasa a CUMPLE cuando el despliegue confirme el certificado; si el puerto 443 está cerrado en el cortafuegos, hay que abrirlo.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NFR-07</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
+          <t>NO EXISTE</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -8311,19 +8311,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
+          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
+          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RF-OPS-001</t>
+          <t>NFR-07</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -8331,31 +8331,31 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lote 2 (avanza)</t>
+          <t>Lote 2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Solo faltan métricas.</t>
+          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RF-GOV-001</t>
+          <t>RF-OPS-001</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -8363,54 +8363,86 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>NO APLICA</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Lote 2 (avanza)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+          <t>Solo faltan métricas.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>RF-GOV-001</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NO CUMPLE</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>NO APLICA</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Fuera del alcance de la tesis por decisión acordada: el piloto corre en un solo servidor.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Para crecer: separar el almacén en un servicio de objetos y varios procesos web.</t>
         </is>

--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -7452,14 +7452,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>[Lote 3 (avanza)] HTTPS sin dominio propio (sslip.io + Let's Encrypt con Caddy), sin caída silenciosa a HTTP (aviso en el despliegue, franja en la interfaz y salud «degradado»), CSP y HSTS solo con HTTPS (app/main.py), contraseña del administrador solo al crear o con RICORA_ADMIN_RESTABLECER=1 (app/cli.py); tests/test_brechas_lote3.py, frontend/src/pruebas/sinCifrar.test.ts. || [Lote 1 (avanza)] Segundo factor y auditoría encadenada. || bcrypt 12 rondas, JWT HS256 con clave ≥32 obligatoria (app/core/seguridad.py:19-135; app/main.py:20-23), bloqueo por intentos (tests/test_autenticacion.py::test_bloqueo_tras_intentos_fallidos), cabeceras nosniff/DENY (app/main.py:89-95), ClamAV, segunda copia ro. HTTPS opcional con retorno a HTTP y galleta no segura (deploy.yml, RICORA_GALLETA_SEGURA 0); sin CSP/HSTS; secretos en .env plano; sin cifrado en reposo; contraseña admin restablecida en cada despliegue; texto documental enviado a Gemini (app/servicios/motor.py:217).</t>
+          <t>[Lote 3] HTTPS sin dominio propio (sslip.io + Let's Encrypt con Caddy), sin caída silenciosa a HTTP (aviso en el despliegue, franja en la interfaz y salud «degradado»), CSP y HSTS solo con HTTPS (app/main.py), contraseña del administrador solo al crear o con RICORA_ADMIN_RESTABLECER=1 (app/cli.py); tests/test_brechas_lote3.py, frontend/src/pruebas/sinCifrar.test.ts. || [Lote 1 (avanza)] Segundo factor y auditoría encadenada. || bcrypt 12 rondas, JWT HS256 con clave ≥32 obligatoria (app/core/seguridad.py:19-135; app/main.py:20-23), bloqueo por intentos (tests/test_autenticacion.py::test_bloqueo_tras_intentos_fallidos), cabeceras nosniff/DENY (app/main.py:89-95), ClamAV, segunda copia ro. HTTPS opcional con retorno a HTTP y galleta no segura (deploy.yml, RICORA_GALLETA_SEGURA 0); sin CSP/HSTS; secretos en .env plano; sin cifrado en reposo; contraseña admin restablecida en cada despliegue; texto documental enviado a Gemini (app/servicios/motor.py:217).</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Despliegue admite HTTP plano, no hay CSP/HSTS, MFA ni cifrado en reposo, y se envía contenido documental a un servicio externo. Avance del Lote 1 (avanza): Segundo factor y auditoría encadenada. Pendiente: Faltan CSP/HSTS, quitar la caída a HTTP y el restablecimiento de la contraseña del administrador en cada despliegue (lote 3). Avance del Lote 3 (avanza): HTTPS sin dominio propio (sslip.io + Let's Encrypt con Caddy), sin caída silenciosa a HTTP (aviso en el despliegue, franja en la interfaz y salud «degradado»), CSP y HSTS solo con HTTPS (app/main.py), contraseña del administrador solo al crear o con RICORA_ADMIN_RESTABLECER=1 (app/cli.py); tests/test_brechas_lote3.py, frontend/src/pruebas/sinCifrar.test.ts. Pendiente: Pasa a CUMPLE cuando el despliegue confirme el certificado; si el puerto 443 está cerrado en el cortafuegos, hay que abrirlo.</t>
+          <t>Cerrada en el Lote 3. Riesgo residual: Confirmado en producción (despliegue 761aaf4: HTTPS activo con certificado verificado). Residual: secreto TOTP sin cifrar, estilos en línea en la CSP, nombre prestado (sslip.io) como base de URI persistentes: fijar dominio institucional antes de publicar.</t>
         </is>
       </c>
     </row>
@@ -8267,14 +8267,14 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lote 3 (avanza)</t>
+          <t>Lote 3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pasa a CUMPLE cuando el despliegue confirme el certificado; si el puerto 443 está cerrado en el cortafuegos, hay que abrirlo.</t>
+          <t>Confirmado en producción (despliegue 761aaf4: HTTPS activo con certificado verificado). Residual: secreto TOTP sin cifrar, estilos en línea en la CSP, nombre prestado (sslip.io) como base de URI persistentes: fijar dominio institucional antes de publicar.</t>
         </is>
       </c>
     </row>

--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -6586,14 +6586,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Solo búsquedas parciales: vocabulario por nombre/trigramas (app/routers/vocabulario.py:143-166), descripciones por título ILIKE (app/routers/descripcion.py:82-89), series (vocabulario.py:217), SPARQL público de solo lectura (app/servicios/sparql.py). No hay búsqueda sobre texto_extraido, alcance, identificadores (codigo_referencia, IdentificadorEntidad) ni índice full-text.</t>
+          <t>[Lote 4] Buscador unificado GET /api/buscar y página Buscar: índice PostgreSQL en español sin tildes (configuración ricora_es, migración 0035) sobre la descripción ISAD(G) y el texto OCR; identificadores (código de referencia, VIAF, ORCID…) completos o por partes; autoridades por nombre y otras formas, con los documentos que las citan; facetas de nivel, años y agente. app/servicios/busqueda.py; tests/test_brechas_lote4.py (palabra solo en el OCR, código de referencia, VIAF). || Solo búsquedas parciales: vocabulario por nombre/trigramas (app/routers/vocabulario.py:143-166), descripciones por título ILIKE (app/routers/descripcion.py:82-89), series (vocabulario.py:217), SPARQL público de solo lectura (app/servicios/sparql.py). No hay búsqueda sobre texto_extraido, alcance, identificadores (codigo_referencia, IdentificadorEntidad) ni índice full-text.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>No existe un buscador unificado de texto completo, metadatos, identificadores y contexto.</t>
+          <t>Cerrada en el Lote 4. Riesgo residual: Un OCR de más de ~1 millón de caracteres se indexa recortado; relevancia menos fina que un motor dedicado.</t>
         </is>
       </c>
     </row>
@@ -6639,14 +6639,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Las consultas existentes exigen sesión y módulo (app/core/permisos.py:156-170) y el catálogo/grafo excluye lo reservado (tests/test_grafo_contexto.py::test_el_perfil_de_consulta_no_ve_lo_reservado_en_el_catalogo_ni_en_las_fichas, tests/test_cierre_bloque4_ins.py::test_sparql_responde_sobre_lo_publico_y_no_ve_lo_reservado). Sin buscador general que verificar ni control por fondo.</t>
+          <t>[Lote 4] La búsqueda usa la misma regla de visibilidad del catálogo, RiC-O, grafo e índice (instrumentos.arbol): el perfil de consulta no recibe nada clasificado o reservado, propio o heredado, ni en resultados, fragmentos, conteos ni autoridades; el texto de un archivo reservado no se consulta. tests/test_brechas_lote4.py (3 pruebas de reserva). || Las consultas existentes exigen sesión y módulo (app/core/permisos.py:156-170) y el catálogo/grafo excluye lo reservado (tests/test_grafo_contexto.py::test_el_perfil_de_consulta_no_ve_lo_reservado_en_el_catalogo_ni_en_las_fichas, tests/test_cierre_bloque4_ins.py::test_sparql_responde_sobre_lo_publico_y_no_ve_lo_reservado). Sin buscador general que verificar ni control por fondo.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Al no existir búsqueda general ni permisos por fondo, no puede demostrarse que la búsqueda respete restricciones en todos los casos.
+          <t>Cerrada en el Lote 4. Riesgo residual: Sin permisos por fondo y persona (RF-GOV-001 fuera de alcance); las búsquedas no se auditan, por decisión (Ley 1581).
 Perfil AGN: incoherencia si un documento con datos sensibles o de menores queda público.</t>
         </is>
       </c>
@@ -8053,7 +8053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8291,12 +8291,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>RF-SEARCH-001</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>NO EXISTE</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -8306,24 +8306,24 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Lote 2</t>
+          <t>Lote 4</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
+          <t>Buscador unificado GET /api/buscar y página Buscar: índice PostgreSQL en español sin tildes (configuración ricora_es, migración 0035) sobre la descripción ISAD(G) y el texto OCR; identificadores (código de referencia, VIAF, ORCID…) completos o por partes; autoridades por nombre y otras formas, con los documentos que las citan; facetas de nivel, años y agente. app/servicios/busqueda.py; tests/test_brechas_lote4.py (palabra solo en el OCR, código de referencia, VIAF).</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
+          <t>Un OCR de más de ~1 millón de caracteres se indexa recortado; relevancia menos fina que un motor dedicado.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NFR-07</t>
+          <t>RF-SEARCH-002</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -8338,56 +8338,56 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Lote 2</t>
+          <t>Lote 4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
+          <t>La búsqueda usa la misma regla de visibilidad del catálogo, RiC-O, grafo e índice (instrumentos.arbol): el perfil de consulta no recibe nada clasificado o reservado, propio o heredado, ni en resultados, fragmentos, conteos ni autoridades; el texto de un archivo reservado no se consulta. tests/test_brechas_lote4.py (3 pruebas de reserva).</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
+          <t>Sin permisos por fondo y persona (RF-GOV-001 fuera de alcance); las búsquedas no se auditan, por decisión (Ley 1581).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RF-OPS-001</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+          <t>NO EXISTE</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lote 2 (avanza)</t>
+          <t>Lote 2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Solo faltan métricas.</t>
+          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RF-GOV-001</t>
+          <t>NFR-07</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -8395,54 +8395,118 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>NO APLICA</t>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Lote 2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>RF-OPS-001</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Lote 2 (avanza)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Solo faltan métricas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RF-GOV-001</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NO CUMPLE</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>NO APLICA</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Fuera del alcance de la tesis por decisión acordada: el piloto corre en un solo servidor.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Para crecer: separar el almacén en un servicio de objetos y varios procesos web.</t>
         </is>
@@ -10814,26 +10878,22 @@
           <t>RF-SEARCH-001</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Solo búsquedas parciales: vocabulario por nombre/trigramas (app/routers/vocabulario.py:143-166), descripciones por título ILIKE (app/routers/descripcion.py:82-89), series (vocabulario.py:217), SPARQL público de solo lectura (app/servicios/sparql.py). No hay búsqueda sobre texto_extraido, alcance, identificadores (codigo_referencia, IdentificadorEntidad) ni índice full-text.</t>
+          <t>[Lote 4] Buscador unificado GET /api/buscar y página Buscar: índice PostgreSQL en español sin tildes (configuración ricora_es, migración 0035) sobre la descripción ISAD(G) y el texto OCR; identificadores (código de referencia, VIAF, ORCID…) completos o por partes; autoridades por nombre y otras formas, con los documentos que las citan; facetas de nivel, años y agente. app/servicios/busqueda.py; tests/test_brechas_lote4.py (palabra solo en el OCR, código de referencia, VIAF). || Solo búsquedas parciales: vocabulario por nombre/trigramas (app/routers/vocabulario.py:143-166), descripciones por título ILIKE (app/routers/descripcion.py:82-89), series (vocabulario.py:217), SPARQL público de solo lectura (app/servicios/sparql.py). No hay búsqueda sobre texto_extraido, alcance, identificadores (codigo_referencia, IdentificadorEntidad) ni índice full-text.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>No existe un buscador unificado de texto completo, metadatos, identificadores y contexto.</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Implementar /api/buscar con tsvector/pg_trgm sobre texto OCR, campos ISAD(G), identificadores y nombres alternativos, con facetas por nivel/fecha/agente.</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 4. Riesgo residual: Un OCR de más de ~1 millón de caracteres se indexa recortado; relevancia menos fina que un motor dedicado.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -10857,26 +10917,22 @@
           <t>RF-SEARCH-002</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Las consultas existentes exigen sesión y módulo (app/core/permisos.py:156-170) y el catálogo/grafo excluye lo reservado (tests/test_grafo_contexto.py::test_el_perfil_de_consulta_no_ve_lo_reservado_en_el_catalogo_ni_en_las_fichas, tests/test_cierre_bloque4_ins.py::test_sparql_responde_sobre_lo_publico_y_no_ve_lo_reservado). Sin buscador general que verificar ni control por fondo.</t>
+          <t>[Lote 4] La búsqueda usa la misma regla de visibilidad del catálogo, RiC-O, grafo e índice (instrumentos.arbol): el perfil de consulta no recibe nada clasificado o reservado, propio o heredado, ni en resultados, fragmentos, conteos ni autoridades; el texto de un archivo reservado no se consulta. tests/test_brechas_lote4.py (3 pruebas de reserva). || Las consultas existentes exigen sesión y módulo (app/core/permisos.py:156-170) y el catálogo/grafo excluye lo reservado (tests/test_grafo_contexto.py::test_el_perfil_de_consulta_no_ve_lo_reservado_en_el_catalogo_ni_en_las_fichas, tests/test_cierre_bloque4_ins.py::test_sparql_responde_sobre_lo_publico_y_no_ve_lo_reservado). Sin buscador general que verificar ni control por fondo.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Al no existir búsqueda general ni permisos por fondo, no puede demostrarse que la búsqueda respete restricciones en todos los casos.</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar el mismo filtro de reserva (derechos.py) y de fondo autorizado dentro del futuro servicio de búsqueda.</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 4. Riesgo residual: Sin permisos por fondo y persona (RF-GOV-001 fuera de alcance); las búsquedas no se auditan, por decisión (Ley 1581).</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>

--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -5822,14 +5822,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Tesseract/pypdfium2 en app/servicios/texto.py:197-229; texto de todas las páginas se concatena con '\n\n' en un único texto_extraido (app/models/instanciacion.py:78). Evidencia de propuesta = fragmento + offset de caracteres (Relacion.fragmento_inicio, app/models/descripcion.py:208-210). Sin página, bloque ni coordenadas; solo confianza media por palabra.</t>
+          <t>[Lote 5] Texto por páginas (paginas_texto) con líneas y caja (OCR desde la tabla de Tesseract; capa de texto: zona buscada en el PDF con pdfium); página y zona de cada fragmento en la propuesta y fijadas en la relación publicada; el visor salta a la página y resalta la línea. app/servicios/texto.py, app/servicios/evidencia.py; tests/test_brechas_lote5.py (PDF escaneado de 3 páginas → página 2 y caja). || Tesseract/pypdfium2 en app/servicios/texto.py:197-229; texto de todas las páginas se concatena con '\n\n' en un único texto_extraido (app/models/instanciacion.py:78). Evidencia de propuesta = fragmento + offset de caracteres (Relacion.fragmento_inicio, app/models/descripcion.py:208-210). Sin página, bloque ni coordenadas; solo confianza media por palabra.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -5840,7 +5840,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>No se conserva la página ni el bloque/coordenadas del texto extraído, solo un offset en el texto concatenado.</t>
+          <t>Cerrada en el Lote 5. Riesgo residual: Documentos anteriores sin páginas hasta ejecutar «python -m app.cli paginar-textos»; la zona es la línea completa.</t>
         </is>
       </c>
     </row>
@@ -6288,14 +6288,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Propuesta lleva motor (modelo) y version_prompt (hash SHA-256, app/servicios/motor.py:166-176); la propuesta se guarda como JSON en TrabajoDescripcion.propuesta (app/models/descripcion.py:240) y al publicar en eventos decision_ia con modelo/version (app/servicios/descripcion.py:568-577); confianza en columnas _Procedencia. No hay tabla de propuestas ni fecha propia de generación.</t>
+          <t>[Lote 5] Tabla propuestas_ia (migración 0036) inalterable por disparador: modelo y versión exacta que respondió, version_prompt, parámetros y tokens, entrada con huella SHA-256 de cada texto enviado, respuesta sin tocar, propuesta controlada, generada_en, duración y estado (generada/publicada/cancelada/expirada); huella de todo el registro; enlazada a trabajo, evaluación, relaciones y decisiones. app/servicios/propuestas_ia.py; tests/test_brechas_lote5.py. || Propuesta lleva motor (modelo) y version_prompt (hash SHA-256, app/servicios/motor.py:166-176); la propuesta se guarda como JSON en TrabajoDescripcion.propuesta (app/models/descripcion.py:240) y al publicar en eventos decision_ia con modelo/version (app/servicios/descripcion.py:568-577); confianza en columnas _Procedencia. No hay tabla de propuestas ni fecha propia de generación.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6306,7 +6306,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>La propuesta no es una entidad persistente propia: vive como texto JSON en el trabajo y como eventos de auditoría al publicar, sin fecha explícita de generación.</t>
+          <t>Cerrada en el Lote 5. Riesgo residual: La respuesta guarda fragmentos de documentos reservados: solo la ve el equipo que describe.</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8355,12 +8355,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>RF-AI-002</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>NO EXISTE</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -8370,24 +8370,24 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lote 2</t>
+          <t>Lote 5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
+          <t>Tabla propuestas_ia (migración 0036) inalterable por disparador: modelo y versión exacta que respondió, version_prompt, parámetros y tokens, entrada con huella SHA-256 de cada texto enviado, respuesta sin tocar, propuesta controlada, generada_en, duración y estado (generada/publicada/cancelada/expirada); huella de todo el registro; enlazada a trabajo, evaluación, relaciones y decisiones. app/servicios/propuestas_ia.py; tests/test_brechas_lote5.py.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
+          <t>La respuesta guarda fragmentos de documentos reservados: solo la ve el equipo que describe.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NFR-07</t>
+          <t>RF-OCR-001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -8402,56 +8402,56 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Lote 2</t>
+          <t>Lote 5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
+          <t>Texto por páginas (paginas_texto) con líneas y caja (OCR desde la tabla de Tesseract; capa de texto: zona buscada en el PDF con pdfium); página y zona de cada fragmento en la propuesta y fijadas en la relación publicada; el visor salta a la página y resalta la línea. app/servicios/texto.py, app/servicios/evidencia.py; tests/test_brechas_lote5.py (PDF escaneado de 3 páginas → página 2 y caja).</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
+          <t>Documentos anteriores sin páginas hasta ejecutar «python -m app.cli paginar-textos»; la zona es la línea completa.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RF-OPS-001</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+          <t>NO EXISTE</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lote 2 (avanza)</t>
+          <t>Lote 2</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Solo faltan métricas.</t>
+          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RF-GOV-001</t>
+          <t>NFR-07</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -8459,54 +8459,118 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>NO APLICA</t>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Lote 2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>RF-OPS-001</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Lote 2 (avanza)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Solo faltan métricas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RF-GOV-001</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NO CUMPLE</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>NO APLICA</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Fuera del alcance de la tesis por decisión acordada: el piloto corre en un solo servidor.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Para crecer: separar el almacén en un servicio de objetos y varios procesos web.</t>
         </is>
@@ -10393,26 +10457,22 @@
           <t>RF-OCR-001</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Tesseract/pypdfium2 en app/servicios/texto.py:197-229; texto de todas las páginas se concatena con '\n\n' en un único texto_extraido (app/models/instanciacion.py:78). Evidencia de propuesta = fragmento + offset de caracteres (Relacion.fragmento_inicio, app/models/descripcion.py:208-210). Sin página, bloque ni coordenadas; solo confianza media por palabra.</t>
+          <t>[Lote 5] Texto por páginas (paginas_texto) con líneas y caja (OCR desde la tabla de Tesseract; capa de texto: zona buscada en el PDF con pdfium); página y zona de cada fragmento en la propuesta y fijadas en la relación publicada; el visor salta a la página y resalta la línea. app/servicios/texto.py, app/servicios/evidencia.py; tests/test_brechas_lote5.py (PDF escaneado de 3 páginas → página 2 y caja). || Tesseract/pypdfium2 en app/servicios/texto.py:197-229; texto de todas las páginas se concatena con '\n\n' en un único texto_extraido (app/models/instanciacion.py:78). Evidencia de propuesta = fragmento + offset de caracteres (Relacion.fragmento_inicio, app/models/descripcion.py:208-210). Sin página, bloque ni coordenadas; solo confianza media por palabra.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>No se conserva la página ni el bloque/coordenadas del texto extraído, solo un offset en el texto concatenado.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Guardar el OCR por página (hOCR/ALTO o TSV de Tesseract) con bloques y bbox, y referenciar página+bloque en la evidencia de cada propuesta.</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 5. Riesgo residual: Documentos anteriores sin páginas hasta ejecutar «python -m app.cli paginar-textos»; la zona es la línea completa.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -10700,26 +10760,22 @@
           <t>RF-AI-002</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Propuesta lleva motor (modelo) y version_prompt (hash SHA-256, app/servicios/motor.py:166-176); la propuesta se guarda como JSON en TrabajoDescripcion.propuesta (app/models/descripcion.py:240) y al publicar en eventos decision_ia con modelo/version (app/servicios/descripcion.py:568-577); confianza en columnas _Procedencia. No hay tabla de propuestas ni fecha propia de generación.</t>
+          <t>[Lote 5] Tabla propuestas_ia (migración 0036) inalterable por disparador: modelo y versión exacta que respondió, version_prompt, parámetros y tokens, entrada con huella SHA-256 de cada texto enviado, respuesta sin tocar, propuesta controlada, generada_en, duración y estado (generada/publicada/cancelada/expirada); huella de todo el registro; enlazada a trabajo, evaluación, relaciones y decisiones. app/servicios/propuestas_ia.py; tests/test_brechas_lote5.py. || Propuesta lleva motor (modelo) y version_prompt (hash SHA-256, app/servicios/motor.py:166-176); la propuesta se guarda como JSON en TrabajoDescripcion.propuesta (app/models/descripcion.py:240) y al publicar en eventos decision_ia con modelo/version (app/servicios/descripcion.py:568-577); confianza en columnas _Procedencia. No hay tabla de propuestas ni fecha propia de generación.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>La propuesta no es una entidad persistente propia: vive como texto JSON en el trabajo y como eventos de auditoría al publicar, sin fecha explícita de generación.</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Crear tabla propuesta_ia (modelo, versión modelo, version_prompt, parámetros, confianza, generada_en, estado) enlazada a trabajo y a decisiones.</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 5. Riesgo residual: La respuesta guarda fragmentos de documentos reservados: solo la ve el equipo que describe.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>

--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5928,14 +5928,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Crear/consultar/editar: POST /api/descripcion/publicar, GET /api/descripcion/registros/{id}, PATCH /api/descripcion/{id} (app/routers/descripcion.py:246,417,561); vocabulario PATCH /api/vocabulario/{id}. Versionado solo como antes/después JSONB en registro_auditoria (tests/test_descripcion.py::test_reabrir_y_editar_queda_en_auditoria_con_antes_y_despues); RecursoDocumental solo tiene actualizado_en.</t>
+          <t>[Lote 6a] Versiones numeradas e inalterables de cada descripción (migración 0037, versiones_descripcion): instantánea de atributos con procedencia y de contexto, autor, fecha y motivo; historial con cambios; restaurar crea una versión nueva. app/servicios/versiones.py; GET/POST /api/descripcion/registros/{id}/versiones…; tests/test_brechas_lote6.py. || Crear/consultar/editar: POST /api/descripcion/publicar, GET /api/descripcion/registros/{id}, PATCH /api/descripcion/{id} (app/routers/descripcion.py:246,417,561); vocabulario PATCH /api/vocabulario/{id}. Versionado solo como antes/después JSONB en registro_auditoria (tests/test_descripcion.py::test_reabrir_y_editar_queda_en_auditoria_con_antes_y_despues); RecursoDocumental solo tiene actualizado_en.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5946,7 +5946,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>No hay versiones consultables/restaurables de entidades: el historial depende del log de auditoría.</t>
+          <t>Cerrada en el Lote 6a. Riesgo residual: Restaurar devuelve atributos, no relaciones (cada relación tiene su propia historia de anulación).</t>
         </is>
       </c>
     </row>
@@ -5981,14 +5981,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Atributos como columnas fijas (app/models/recurso_documental.py:47-104); fuente/confianza solo para título, alcance e idiomas (origen_titulo, origen_alcance, confianza_*), y _Procedencia para entidades/relaciones (app/models/descripcion.py:65-78). Perfil de cardinalidades RiC-O documentado: tests/test_ric_o.py::test_el_perfil_de_cardinalidades_esta_escrito_y_documentado.</t>
+          <t>[Lote 6a] Catálogo de atributos (app/servicios/atributos.py): tipo, cardinalidad, ISAD(G), RiC-O y procedencia; validación de cardinalidad al publicar y corregir; vista interna atributo · valor · fuente · confianza. tests/test_brechas_lote6.py. || Atributos como columnas fijas (app/models/recurso_documental.py:47-104); fuente/confianza solo para título, alcance e idiomas (origen_titulo, origen_alcance, confianza_*), y _Procedencia para entidades/relaciones (app/models/descripcion.py:65-78). Perfil de cardinalidades RiC-O documentado: tests/test_ric_o.py::test_el_perfil_de_cardinalidades_esta_escrito_y_documentado.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>No hay gestión de atributos (tipo, cardinalidad, fuente) por atributo: el esquema es fijo y la fuente solo existe para algunos campos.
+          <t>Cerrada en el Lote 6a. Riesgo residual: La procedencia de los atributos que el motor no propone se deduce («persona»); autor y fecha en las versiones.
 Perfil AGN: estado de conservación y signatura topográfica del original físico (migración 0031).</t>
         </is>
       </c>
@@ -8053,7 +8053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8419,12 +8419,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>RF-RIC-001</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>NO EXISTE</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -8434,24 +8434,24 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lote 2</t>
+          <t>Lote 6a</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
+          <t>Versiones numeradas e inalterables de cada descripción (migración 0037, versiones_descripcion): instantánea de atributos con procedencia y de contexto, autor, fecha y motivo; historial con cambios; restaurar crea una versión nueva. app/servicios/versiones.py; GET/POST /api/descripcion/registros/{id}/versiones…; tests/test_brechas_lote6.py.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
+          <t>Restaurar devuelve atributos, no relaciones (cada relación tiene su propia historia de anulación).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NFR-07</t>
+          <t>RF-RIC-002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -8466,56 +8466,56 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Lote 2</t>
+          <t>Lote 6a</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
+          <t>Catálogo de atributos (app/servicios/atributos.py): tipo, cardinalidad, ISAD(G), RiC-O y procedencia; validación de cardinalidad al publicar y corregir; vista interna atributo · valor · fuente · confianza. tests/test_brechas_lote6.py.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
+          <t>La procedencia de los atributos que el motor no propone se deduce («persona»); autor y fecha en las versiones.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RF-OPS-001</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+          <t>NO EXISTE</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Lote 2 (avanza)</t>
+          <t>Lote 2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Solo faltan métricas.</t>
+          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RF-GOV-001</t>
+          <t>NFR-07</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -8523,54 +8523,118 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>NO APLICA</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Lote 2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>RF-OPS-001</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Lote 2 (avanza)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Solo faltan métricas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>RF-GOV-001</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NO CUMPLE</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>NO APLICA</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fuera del alcance de la tesis por decisión acordada: el piloto corre en un solo servidor.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Para crecer: separar el almacén en un servicio de objetos y varios procesos web.</t>
         </is>
@@ -10539,26 +10603,22 @@
           <t>RF-RIC-001</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Crear/consultar/editar: POST /api/descripcion/publicar, GET /api/descripcion/registros/{id}, PATCH /api/descripcion/{id} (app/routers/descripcion.py:246,417,561); vocabulario PATCH /api/vocabulario/{id}. Versionado solo como antes/después JSONB en registro_auditoria (tests/test_descripcion.py::test_reabrir_y_editar_queda_en_auditoria_con_antes_y_despues); RecursoDocumental solo tiene actualizado_en.</t>
+          <t>[Lote 6a] Versiones numeradas e inalterables de cada descripción (migración 0037, versiones_descripcion): instantánea de atributos con procedencia y de contexto, autor, fecha y motivo; historial con cambios; restaurar crea una versión nueva. app/servicios/versiones.py; GET/POST /api/descripcion/registros/{id}/versiones…; tests/test_brechas_lote6.py. || Crear/consultar/editar: POST /api/descripcion/publicar, GET /api/descripcion/registros/{id}, PATCH /api/descripcion/{id} (app/routers/descripcion.py:246,417,561); vocabulario PATCH /api/vocabulario/{id}. Versionado solo como antes/después JSONB en registro_auditoria (tests/test_descripcion.py::test_reabrir_y_editar_queda_en_auditoria_con_antes_y_despues); RecursoDocumental solo tiene actualizado_en.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>No hay versiones consultables/restaurables de entidades: el historial depende del log de auditoría.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Crear tablas de versión (o temporal tables) por entidad con número de versión y endpoint GET /versiones y restauración.</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 6a. Riesgo residual: Restaurar devuelve atributos, no relaciones (cada relación tiene su propia historia de anulación).</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -10582,26 +10642,22 @@
           <t>RF-RIC-002</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Atributos como columnas fijas (app/models/recurso_documental.py:47-104); fuente/confianza solo para título, alcance e idiomas (origen_titulo, origen_alcance, confianza_*), y _Procedencia para entidades/relaciones (app/models/descripcion.py:65-78). Perfil de cardinalidades RiC-O documentado: tests/test_ric_o.py::test_el_perfil_de_cardinalidades_esta_escrito_y_documentado.</t>
+          <t>[Lote 6a] Catálogo de atributos (app/servicios/atributos.py): tipo, cardinalidad, ISAD(G), RiC-O y procedencia; validación de cardinalidad al publicar y corregir; vista interna atributo · valor · fuente · confianza. tests/test_brechas_lote6.py. || Atributos como columnas fijas (app/models/recurso_documental.py:47-104); fuente/confianza solo para título, alcance e idiomas (origen_titulo, origen_alcance, confianza_*), y _Procedencia para entidades/relaciones (app/models/descripcion.py:65-78). Perfil de cardinalidades RiC-O documentado: tests/test_ric_o.py::test_el_perfil_de_cardinalidades_esta_escrito_y_documentado.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>No hay gestión de atributos (tipo, cardinalidad, fuente) por atributo: el esquema es fijo y la fuente solo existe para algunos campos.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Definir un catálogo de atributos con tipo/cardinalidad y registrar procedencia por atributo (o tabla atributo_valor con origen).</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 6a. Riesgo residual: La procedencia de los atributos que el motor no propone se deduce («persona»); autor y fecha en las versiones.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>

--- a/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
+++ b/documentacion/RICORA_MATRIZ_MAESTRA_REQUISITOS_v3_0_auditada.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -7191,14 +7191,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI autogenerado por FastAPI en /api/openapi.json y /api/docs (app/main.py:26-35) con tags y summary para dominio, preservación y auditoría. Muchas rutas devuelven dict sin response_model (p. ej. app/routers/preservacion.py:82-395, app/routers/auditoria.py:56-274) y ningún test valida el contrato OpenAPI.</t>
+          <t>[Lote 6b] Las 193 operaciones (178 rutas) declaran su respuesta en OpenAPI (esquema JSON o tipo de archivo; app/schemas/respuestas_*.py). Prueba de contrato: cada respuesta real de la batería se valida contra el esquema de su ruta (tests/contrato.py, ClienteConContrato); tests/test_contrato_api.py exige esquema, resumen y etiqueta en toda ruta. /api/v1 es alias estable y X-API-Version: 1. || OpenAPI autogenerado por FastAPI en /api/openapi.json y /api/docs (app/main.py:26-35) con tags y summary para dominio, preservación y auditoría. Muchas rutas devuelven dict sin response_model (p. ej. app/routers/preservacion.py:82-395, app/routers/auditoria.py:56-274) y ningún test valida el contrato OpenAPI.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -7209,7 +7209,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>La documentación OpenAPI existe pero con esquemas de respuesta incompletos y sin verificación automática ni versionado de API.</t>
+          <t>Cerrada en el Lote 6b. Riesgo residual: Una ruta que ninguna prueba llama no se valida en ejecución; los campos más variables quedan como objeto genérico.</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8483,12 +8483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>RF-INT-003</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>NO EXISTE</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -8498,29 +8498,29 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Lote 2</t>
+          <t>Lote 6b</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
+          <t>Las 193 operaciones (178 rutas) declaran su respuesta en OpenAPI (esquema JSON o tipo de archivo; app/schemas/respuestas_*.py). Prueba de contrato: cada respuesta real de la batería se valida contra el esquema de su ruta (tests/contrato.py, ClienteConContrato); tests/test_contrato_api.py exige esquema, resumen y etiqueta en toda ruta. /api/v1 es alias estable y X-API-Version: 1.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
+          <t>Una ruta que ninguna prueba llama no se valida en ejecución; los campos más variables quedan como objeto genérico.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NFR-07</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
+          <t>NO EXISTE</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -8535,19 +8535,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
+          <t>Cinco escenarios con RPO/RTO objetivo (parámetros) frente a lo medido: app/servicios/recuperacion.py::estado; Preservación › Configuración › Recuperación ante desastres; tests/test_brechas_lote2.py::test_rpo_y_rto_por_escenario_frente_a_lo_medido.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
+          <t>El tiempo de instalar un servidor nuevo es estimado (2 h), no medido.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RF-OPS-001</t>
+          <t>NFR-07</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -8555,31 +8555,31 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lote 2 (avanza)</t>
+          <t>Lote 2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
+          <t>Paquete de recuperación (base + archivos + manifiesto con huellas, en la misma instantánea) y simulacro integral en base y carpeta nuevas con verificación de filas, huellas y cadena de auditoría; CLI restaurar-paquete; migración 0034; tests/test_brechas_lote2.py.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Solo faltan métricas.</t>
+          <t>El simulacro corre en el mismo servidor; la restauración en otro servidor se hace con la orden documentada.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RF-GOV-001</t>
+          <t>RF-OPS-001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -8587,54 +8587,86 @@
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>NO APLICA</t>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Lote 2 (avanza)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+          <t>Copia completa fuera del servidor: el paquete descargable lleva la base y los archivos; su descarga se registra y mide el RPO.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+          <t>Solo faltan métricas.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>RF-GOV-001</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Fuera del alcance de la tesis por decisión acordada: varias organizaciones en un mismo sistema no es exigencia del AGN ni aporta al piloto.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Si se despliega para varias entidades, cada una usa su propia instancia (docker-compose).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NO CUMPLE</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>NO APLICA</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Decisión</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fuera del alcance de la tesis por decisión acordada: el piloto corre en un solo servidor.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Para crecer: separar el almacén en un servicio de objetos y varios procesos web.</t>
         </is>
@@ -11354,26 +11386,22 @@
           <t>RF-INT-003</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>OpenAPI autogenerado por FastAPI en /api/openapi.json y /api/docs (app/main.py:26-35) con tags y summary para dominio, preservación y auditoría. Muchas rutas devuelven dict sin response_model (p. ej. app/routers/preservacion.py:82-395, app/routers/auditoria.py:56-274) y ningún test valida el contrato OpenAPI.</t>
+          <t>[Lote 6b] Las 193 operaciones (178 rutas) declaran su respuesta en OpenAPI (esquema JSON o tipo de archivo; app/schemas/respuestas_*.py). Prueba de contrato: cada respuesta real de la batería se valida contra el esquema de su ruta (tests/contrato.py, ClienteConContrato); tests/test_contrato_api.py exige esquema, resumen y etiqueta en toda ruta. /api/v1 es alias estable y X-API-Version: 1. || OpenAPI autogenerado por FastAPI en /api/openapi.json y /api/docs (app/main.py:26-35) con tags y summary para dominio, preservación y auditoría. Muchas rutas devuelven dict sin response_model (p. ej. app/routers/preservacion.py:82-395, app/routers/auditoria.py:56-274) y ningún test valida el contrato OpenAPI.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>La documentación OpenAPI existe pero con esquemas de respuesta incompletos y sin verificación automática ni versionado de API.</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Declarar response_model/ejemplos en todas las rutas, versionar (/api/v1) y añadir prueba que valide openapi.json (p. ej. schemathesis).</t>
-        </is>
-      </c>
+          <t>Cerrada en el Lote 6b. Riesgo residual: Una ruta que ninguna prueba llama no se valida en ejecución; los campos más variables quedan como objeto genérico.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
